--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3816,6 +3816,84 @@
         <v>51</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6439.31982421875</v>
+      </c>
+      <c r="C44" t="n">
+        <v>6466.89013671875</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6438.06005859375</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6457.669921875</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4059070000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.0042663855480634</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>inventhelp inventor develop new thermal capacitor water heater tl council asked to help expand eye on the street program gray medium to produce and air tomorrow new orleans saint preseason game in endtoend native hdr via nextgen tv hidden google search feature that make you a power user jerome powell signal fed may cut rate soon even a inflation risk remain elon musk must face lawsuit for duping trump supporter in million giveaway give your teeth the care they deserve with off an aquasonic ultra whitening toothbrush u supreme court allows nih to cut billion in research grant nature ninepoint partner announces estimated august cash distribution for ninepoint cash management fund etf series clean smarter not harder the best electric spin scrubber make cleaning a breeze federal workforce to lose employee this year trump official say in canada billboard woman in music open nomination for honoree cracker barrel crackup how the culture war are upending corporate branding powell signal fed may cut rate soon even a inflation risk remain canada will match u tariff exemption under usmca trade pact prime minister carney say whats needed to unlock the power and promise of imec new rv provides opioid recovery medical care to underserved minneapolis neighborhood powell signal fed may cut rate soon even a inflation risk remain onlyfans stats that show how massive the platform ha become green space are key to combating record heat in marginalized community familyfriendly workplace gov order budget cut for all state agency except school why xrp is soaring today are you even ready to grow lesson every owneroperator need before adding a truck gen z career catfishing rise ai recruiter a ethical solution trump say canada will drop usmcacompliant retaliatory tariff capital solution hire former caci exec a chief operating officer sunflower elect new board leader director king island tease return of beloved phantom theater ride top evercore analyst boost nvidia nvda stock price target ahead of q earnings tipranks bank lobby for national standard to limit state regulation shareholder alert levi korsinsky llp notifies investor it ha filed a complaint to recover loss suffered by purchaser of cai inc security and set a lead plaintiff deadline of october rosen national investor counsel encourages lockheed martin corporation investor to secure counsel before important deadline in security class action lmt elite express holding inc announces closing of million initial public offering ross benefit from value shopper but tariff challenge continue cvcc board set to review tax implication of new career center best ai writing tool for researcher zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice canada to ease most retaliatory tariff against united state extrump cfo weisselberg may keep severance pay appellate court rule ethylene buyer could be ruined for their cartel example of unpaid work deal dispatch muskaltman drama ashton kutcher soho house play and we pose question to private equity pro fiserv push embedded payment for health care canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal netskope file for u ipo with m revenue yoy growth walmart q revenue surge to b raise fullyear outlook delta airline offering new direct flight from austin airport why intuit stock intu is sinking today blue bell ice cream recalled due to packaging error trump say hell be very good to canada a it prime minister drop some tariff trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u npr trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u weekly commodity wrapup why lucid group stock died today then got better tinley park chamber cancel this year oktoberfest due to cost how market reacted after powell signaled potential rate cut eastgroup property announces dividend increase how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war branded legacy inc form strategic partnership with stanford university dr eran bendavid to advance addiction solution stock market surge after jerome powell indicates rate cut may be coming canada remove countertariffs on some u good canada to drop countertariffs on some u good one day after call with trump bitcoin and crypto stock surge a powell ratecut hint revives risk appetite walmart hike discount for shopper amid tariff uncertainty this is what whale are betting on okta starbucks car toy close on broadway in denver coffee giant closing all non drivethrus snap investor with loss in excess of k have opportunity to lead snap inc security lawsuit kirby mcinerney llp announces investigation against avita medical inc on behalf of investor bear alley marketing position itself a a leader in performance marketing for home service trump say hell keep extending tiktok shutdown deadline let talk indianola school business official brian bartz what is credit card forbearance and who qualifies for it this september bet bonus code nypbet bet get in bonus bet win or lose for yankee v red sox on friday sima monthly investment fund statistic july pi down from ath icp volume tank meanwhile blockdags b token sold point to the next x dsw offer discount on brook revel running shoe this week degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc brattleboro parking zone to be relabeled high roller announces nyse acceptance of plan to regain listing compliance degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc canada to remove many retaliatory tariff on u good allegro stock recovery elliott wave structure support fundamental case labubu blind box restocking aug aug here what to know trump say intel ha agreed to give the u a equity stake bloomberg rich lowry trump is wrong about mailin voting cheap drug high stake america risky bet on china trump again give putin a couple of week with no sign of ukraine peace talk underway cnn trump suggests chicago is next for federal crime crackdown followed by new york city cbs news president donald trump plan crime crackdown in chicago similar to dc national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital court ruling clear the way for hundred of cdc staff to be laid off jury selection taking time in randolph csc trial mayor trump president fixates on local crime asphalt and lamppost latest news on fbi searching john boltons home office george mason illegally used race in hiring department of education find george mason illegally used race in hiring department of education find a judge ha ordered alligator alcatraz in florida to wind down operation what happens now world cup draw will be held at washington kennedy center trump say kamala harris will take her day book tour to los angeles california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk newsoms profile soar with trump redistricting fight california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk lake lynn answer ferc question raise possibility of entry fee at cheat lake park people officially became u citizen at the new york state fair funeral home owner who stashed nearly decaying body set to be sentenced new york city to get federal police for crime crackdown after dc chicago trump trump praise missouri republican for considering redistricting bolton investigated over classified document not politics vp vance tell nbc community patrol confronts ice officer at city height elementary school parking lot stitt take aim at tulsa mayor decision to prosecute crime in tribal court trump tariff will reduce deficit by trillion over next decade say cbo report ask rusty how do i apply for s and receive my payment trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline uk diplomat receives warning over illegal fishing with jd vance mit global collapse warning revisited humanity enters makeorbreak decade chicago is up next for the national guard theyre screaming for u say trump san carlos and the lastminute commissioner item henderson accepting application for addition to veteran memorial wall trump reacts to canada reversing retaliatory tariff take question at white house erik and lyle menendez can still walk free from prison even if both brother have parole denied a family fight back desantis fire back after dem decries florida move to ditch lgbt rainbow color from crosswalk in orlando hegseth authorizes national guard to carry gun in washington dc ap technology summarybrief at pm edt trump is astonishingly deluded about putin trump official demand apology from george mason president over diversity the new york time the u air force just underwent a massive stress test of how it would fight a highend war in the pacific uk top diplomat get a warning for illegal fishing with u vice president national guard troop in washington will be armed hegseth matt fleming how assembly democrat came to embrace gerrymandering passing the baton in europe could donald trump really win the nobel peace prize asking eric am i wrong for wanting to back out of mexican vacation now that friend included her son beware of the skeeters and malary asking eric am i wrong for backing out of a trip because a friend son is going an energy transition at the crossroad south korea journey toward resilience the u navy drone effort arent going wellbut neither are china pa budget stall again what will it take to break the cycle of delay carney say he will travel to germany next week to deepen tie canada go learn some english customer berates georgian nyc cafe owner now everyones coming to her defense teaching just the fact is not an answer to indoctrination gavin newsoms redistricting gambit a presidential audition not a policy plan fifa world cup draw to take place at kennedy center trump announces tension flare a texas house panel hears a bathroom bill for first time in eight year trump message to dc criminal democrat dont mess with me how some apps are working to solve the epidemic of loneliness what to expect from the ussouth korea summit planned parenthood sue south carolina over medicaid ban certain local voice oppose gov newsoms redistricting campaign cracker barrel new logo sucksand not because of wokeness you idiot ct governor directs flag to halfstaff saturday for state employee fatally injured on job trump say hell ask congress for b for dc improvement letter taxpayer against genocide trump say putin may attend north america world cup it so on after heated back and forth with chris rufo on conservatism jonah goldberg agrees to debate homeowner oppose plan for fencing dune on hollywood beach here why trump say putin may attend north america world cup california ab stall in senate amid parental right opposition trump say putin may attend north america world cup trump say putin may attend north america world cup california governor signed a redistricting plan what happens next trump show off photo putin mailed him from alaska summit but president warns i better be very happy with peace talk after russia ukraine attack policy review committee recap august james jim mcgregor trump say chicago is next for dcstyle federal law enforcement operation a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now shiba inu shib is taking longer than expected to reach new high in pepe coin pepe and this coin to outperform it investing in ozak ai ethereumbased ai token during it under presale could lead to millionaire status by a btc and eth hit ath cadence bank ha million stock holding in texas instrument incorporated txn jpmorgan chase co jpm share sold by rbo co llc hoka ha shoe on sale for a low a right now including bondi and clifton trump administration halt construction of revolution wind farm off mass citing national security new brewery tap into corydons dora ordinance excitement british columbia investment management corp sell share of alphabet inc goog british columbia investment management corp raise holding in broadcom inc avgo air canada say more passenger eligible for reimbursement if flight were cancelled canada grab these safe djia dividend bargain after index hit alltime high nextgen pick best cryptos to buy today a arctic pablos cex listing driving maximum gain potential twothirds of river trash is plastic research fastfood chain lock in meal to fight inflation in newsguild see organizing surge a medium worker fuel grassroots militancy tech ceo urge dignity for billion shift worker amid automation lowes target pro with total home strategy amid sale dip and inflation european postal service halt u shipment over trump tariff china stock surge defies weak economy raising fear of another bust analyst waste management inc nysewm announces quarterly dividend evans city council approves ballot language for permanent road tax bet bonus code orl bonus for seahawks v packer raider v cardinal solana whale rotate capital into layer brett analyst say it could deliver x gain by next year whale are choosing this meme coin a the best crypto to buy in instead of dogecoin doge and shiba sol strengthens on institutional demand xrp jump after whale action and blockdags forecast draw buyer in phoenix wealth advisor sell share of air product and chemical inc apd btc climbed to of global money before fed chair signaled rate cut cointelegraph heritage wealth partner llc buy share of meta platform inc meta palantir technology nasdaqpltr insider ryan taylor sell share palantir technology nasdaqpltr insider ryan taylor sell share of stock promising retail stock to keep an eye on august th jpmorgan chase co jpm is biondo investment advisor llcs th largest position immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say trump appeal in fraud case likely despite his total victory trump appeal in fraud case likely despite his total victory baby boomer turned meme stock trading into a thrilling hobby calling it absolutely gambling trump appeal in fraud case likely despite his total victory this weatherproof storage shed is only during wayfairs labor day blowout sale bank of america nysebac hit new month high whats next invesco qqq qqq share purchased by haverford trust co cardano price prediction ada eye new high yet this lowcap coin ha x more upside beltway buzz august apg asset management nv acquires share of intuitive surgical inc isrg pfizer inc pfe share sold by apg asset management nv what to know about visa for foreign trucker and the politics of a deadly florida crash the best amazon deal to shop right now save up to trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete bitcoin btc price could retrace before a run toward kk but ripple xrp and this coin are aiming high in cryptos next top altcoin why this crypto could shine a xrp fall below best gift for digital artist in trump halt work on nearly complete new england offshore wind project waste management inc wm share acquired by groupe la francaise union pacific corporation unp share purchased by kestra advisory service llc haverford trust co sell share of unitedhealth group incorporated unh waste management inc wm share sold by van hulzen asset management llc groupe la francaise purchase share of walmart inc wmt phoenix wealth advisor trim position in cisco system inc csco bahl gaynor inc increase stake in taiwan semiconductor manufacturing company ltd tsm best of the best bahl gaynor inc sell share of mcdonalds corporation mcd chicago a mess trump vow national guard crackdown layer brett dubbed pepe after early momentum outpaces early doge and shib launch hooter bankruptcy prompt rebrand to tacky familyfriendly are home depot cheapest tool set worth buying here what user say trump halt work on new england offshore wind project thats nearly complete douglas winthrop advisor llc sell share of pepsico inc pep caitlin john llc ha holding in invesco qqq qqq british columbia investment management corp buy share of procter gamble company the pg penticton council willing to work with art gallery after layoff announced penticton get your own steam locomotive how family can save money this backtoschool season northwest minnesota foundation issue over million in grant loan during th quarter why the iea reinstated it business a usual scenario business accelerator academy start in september how u of a help build worldclass entrepreneur dogecoin price target in september but analyst say x gain belong to new lowcaps can solana reach by or is there a better crypto to buy now blockdags m presale and referral reward shift focus from xrp rally and eth market issue trump halt work on new england offshore wind project thats nearly complete yahoocom trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete ai bubble fear spark tech stock slide crash warning rise how and where to bet mlb player prop pick odds for aug garrett crochet among best bet smartleaf asset management llc ha million stock holding in mastercard incorporated ma walmart nysewmt issue fy earnings guidance biondo investment advisor llc ha million stake in unitedhealth group incorporated unh cadence bank sell share of american express company axp forest avenue capital management lp boost holding in vistra corp vst european post suspend u delivery over trumpera tariff biondo investment advisor llc acquires share of amgen inc amgn svb wealth llc lower stock position in blackrock blk svb wealth llc sell share of air product and chemical inc apd air product and chemical inc apd share sold by british columbia investment management corp svb wealth llc sell share of air product and chemical inc apd lionshead wealth management llc ha holding in illinois tool work inc itw biondo investment advisor llc increase stock holding in duke energy corporation duk kruse out a dia director in latest pentagon shakeup cringe watch zohran mamdani plan nyc scavenger hunt is there a prize if youre mugged on the subway cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened u justice department release transcript of interview with ghislaine maxwell kilmar abrego garcia is freed from tennessee jail so he can rejoin family in maryland to await trial greene issue scathing rebuke of condition in gaza i will not be silent about it israel vow to open gate of hell on gaza in chilling warning a famine grip the region u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case kevin oleary sound alarm on rich kid upbringing they become lost in a sea of mediocrity it a disaster for them former dhs official signal he could be next after bolton fbi raid we expect it the lioness at the center of a city hall battered by scandal dnc vote on israel arm embargo may set democratic party course on palestine trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it u seek to deport abrego garcia to uganda hampton county law enforcement to ramp up duo patrol trump administration considering deporting kilmar abrego garcia to uganda his lawyer say secretariat jockey mourned in maine a well a canada dunkin customer warns to check receipt after spotting wellness fee national guard roll out in state not linked to trump crime crackdown wh say the redistricting war between texas and california is about to jolt the midterm politico asking eric were no longer invited to shared family holiday meal what should we do about upcoming wedding redistricting war poised to explode a california and texas make their move la consequential karen bass earns epic ratio over claim city recovery is fastest in state history the redistricting war between texas and california is about to jolt the midterm texas abbott promise quick signature of redistricting plan following overnight senate vote ghislaine maxwell absolves trump and everyone else in doj interview conservative activist slam cracker barrel a company left reeling after logo redesign south korea japan agree to boost tie a challenge mount kilmar abrego garcia released from ice custody after return from el salvador truck driver in crash at center of trump administration feud with newsom is denied bond when trying to explain low dem party polling look no further than awesome duo of newsom and swalwell immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case trump look to chicago next in federal crackdown the wall street journal giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell university of oregon concludes law review discriminated based on perceived national origin against israeli author trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress how redistricting is done and why it could give party an edge in election how redistricting is done and why it could give party an edge in election democrat mock jd vance for having cardboard charisma a he push unpopular budget bill opinion it time for mayo pete buttigieg to find some seasoning what happened to ambition for bay restoration guest commentary kilmar abrego garcia threatened with deportation to uganda larimer county restaurant inspection made aug kilmar abrego garcia threatened with deportation to uganda kilmar abrego garcia threatened with deportation to uganda judge block trump from cutting funding from city and county including denver over sanctuary policy internet tax freedom act preempt new york imposition of tax fbi target john boltons home and office trump he not a smart guy but he could be a very unpatriotic guy inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal rachel bitecofer warns that bolton is just the start and trump will go after the rest of u inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal what we know about china and russia new strategic bomber inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal zelenskyy say security guarantee for ukraine to be ready soon bill maher applauds gavin newsom for mocking donald trump i think it very funny floridarun alligator alcatraz violates u law aclu say russia announces support for venezuela to defend sovereignty amid growing military tension with the united state gianno caldwell mull senate bid a chicagoans are begging for change on crime woe trump threatens chicago with next national guard invasion cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview the owl eye liberty and memory from epstein suicide to trump and clinton takeaway from ghislaine maxwell transcript how can israel engineer a famine in gaza in the st century what we learned from the ghislaine maxwell doj interview texas gov abbott say hell swiftly sign redistricting map after lawmaker approve them jeff bezos said he would have felt icky had he taken any more share of amazon i just didnt feel good smart money strategy what the pro buy when the crypto market crash radioactive shrimp update walmart store brand and other brand recalled european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff a winning powerball ticket ha been sold in western new york the sp hasnt yielded this little since the dotcom bubble here what investor can do the motley fool just ranked the biggest financial stock here why the no pick could be your best investment mezcal producer preserve traditional method a demand for liquor grows minute european postal service suspend shipment of package to u over tariff kpop demon hunter give netflix it first boxoffice win curry join the bank holiday sale bonanza with it epic deal event here are the best offer id buy self driving taxi may be coming to nyc a waymo win first av testing permit mashable rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important deadline in security class action fi ice cream sold at walmarts across state recalled due to undeclared allergen here how a gamestop purchase turned into a bitcoin jackpot ice cream sold at walmarts across state recalled due to undeclared allergen fox business prediction lucid group sale will soar over the next year if this happens solar executive warn that trump attack on renewables will lead to power crunch that spike electricity price pueblo county home listing asked for less money in july see the current median price here prediction these trilliondollar artificial intelligence ai stock could strike a megadeal that wall street isnt ready for cold wallet cashback utility and presale pricing create a upside case while chainlink and shiba inu struggle maintenance compliance burden viability of hopi water treatment system ethereum in trouble xrp might breakout buyer turn to blockdag to earn referral reward acting a the executor of a will can be a very lucrative job the last word national guard troop to be force multiplier for ice homan little pepe crypto price prediction is lilpepe a good investment for longterm holder here how much you should aim to invest in the invesco qqq etf to get to million or more by retirement state audit question m in federal spending by moses lake school district blockchain stock worth watching august th owner scale back golden mile shopping center redevelopment rosen global investor counsel encourages easterly rocmuni high income municipal bond fund comerica bank lower stake in alphabet inc goog trump tap airbnb cofounder a st government design head to lead huge web overhaul trump tap airbnb cofounder a st government design head to lead huge web overhaul fox business offgrid living next new real estate trend a application for rural mortgage skyrocket rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before epstein accuser virginia giuffre wrote a memoir month after her death it coming out powell warning signal unemployment claim jump to highest in year cardano price outlook can ada reach trumprelated defi platform world liberty financial debut wlfi token on ethereum mainnet rosen global investor counsel encourages altimmune inc investor to secure counsel before important deadline in security class action alt the best meme coin presale stampede is loading whitelist labubull now or watch it moon without you backtoschool deal tellos unlimited plan get you cell service for per month your first month nexus gold cvenxs stock price up whats next mason resource cvellg stock price up here why mason resource cvellg trading up here what happened national guard troop to be force multiplier for ice homan freedom investment management inc purchase share of procter gamble company the pg ascent group llc raise stock holding in ameri</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>inventhelp inventor develop new thermal capacitor water heater tl council asked to help expand eye on the street program gray medium to produce and air tomorrow new orleans saint preseason game in endtoend native hdr via nextgen tv hidden google search feature that make you a power user jerome powell signal fed may cut rate soon even a inflation risk remain elon musk must face lawsuit for duping trump supporter in million giveaway give your teeth the care they deserve with off an aquasonic ultra whitening toothbrush u supreme court allows nih to cut billion in research grant nature ninepoint partner announces estimated august cash distribution for ninepoint cash management fund etf series clean smarter not harder the best electric spin scrubber make cleaning a breeze federal workforce to lose employee this year trump official say in canada billboard woman in music open nomination for honoree cracker barrel crackup how the culture war are upending corporate branding powell signal fed may cut rate soon even a inflation risk remain canada will match u tariff exemption under usmca trade pact prime minister carney say whats needed to unlock the power and promise of imec new rv provides opioid recovery medical care to underserved minneapolis neighborhood powell signal fed may cut rate soon even a inflation risk remain onlyfans stats that show how massive the platform ha become green space are key to combating record heat in marginalized community familyfriendly workplace gov order budget cut for all state agency except school why xrp is soaring today are you even ready to grow lesson every owneroperator need before adding a truck gen z career catfishing rise ai recruiter a ethical solution trump say canada will drop usmcacompliant retaliatory tariff capital solution hire former caci exec a chief operating officer sunflower elect new board leader director king island tease return of beloved phantom theater ride top evercore analyst boost nvidia nvda stock price target ahead of q earnings tipranks bank lobby for national standard to limit state regulation shareholder alert levi korsinsky llp notifies investor it ha filed a complaint to recover loss suffered by purchaser of cai inc security and set a lead plaintiff deadline of october rosen national investor counsel encourages lockheed martin corporation investor to secure counsel before important deadline in security class action lmt elite express holding inc announces closing of million initial public offering ross benefit from value shopper but tariff challenge continue cvcc board set to review tax implication of new career center best ai writing tool for researcher zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice canada to ease most retaliatory tariff against united state extrump cfo weisselberg may keep severance pay appellate court rule ethylene buyer could be ruined for their cartel example of unpaid work deal dispatch muskaltman drama ashton kutcher soho house play and we pose question to private equity pro fiserv push embedded payment for health care canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal netskope file for u ipo with m revenue yoy growth walmart q revenue surge to b raise fullyear outlook delta airline offering new direct flight from austin airport why intuit stock intu is sinking today blue bell ice cream recalled due to packaging error trump say hell be very good to canada a it prime minister drop some tariff trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u npr trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u weekly commodity wrapup why lucid group stock died today then got better tinley park chamber cancel this year oktoberfest due to cost how market reacted after powell signaled potential rate cut eastgroup property announces dividend increase how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war branded legacy inc form strategic partnership with stanford university dr eran bendavid to advance addiction solution stock market surge after jerome powell indicates rate cut may be coming canada remove countertariffs on some u good canada to drop countertariffs on some u good one day after call with trump bitcoin and crypto stock surge a powell ratecut hint revives risk appetite walmart hike discount for shopper amid tariff uncertainty this is what whale are betting on okta starbucks car toy close on broadway in denver coffee giant closing all non drivethrus snap investor with loss in excess of k have opportunity to lead snap inc security lawsuit kirby mcinerney llp announces investigation against avita medical inc on behalf of investor bear alley marketing position itself a a leader in performance marketing for home service trump say hell keep extending tiktok shutdown deadline let talk indianola school business official brian bartz what is credit card forbearance and who qualifies for it this september bet bonus code nypbet bet get in bonus bet win or lose for yankee v red sox on friday sima monthly investment fund statistic july pi down from ath icp volume tank meanwhile blockdags b token sold point to the next x dsw offer discount on brook revel running shoe this week degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc brattleboro parking zone to be relabeled high roller announces nyse acceptance of plan to regain listing compliance degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc canada to remove many retaliatory tariff on u good allegro stock recovery elliott wave structure support fundamental case labubu blind box restocking aug aug here what to know trump say intel ha agreed to give the u a equity stake bloomberg rich lowry trump is wrong about mailin voting cheap drug high stake america risky bet on china trump again give putin a couple of week with no sign of ukraine peace talk underway cnn trump suggests chicago is next for federal crime crackdown followed by new york city cbs news president donald trump plan crime crackdown in chicago similar to dc national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital court ruling clear the way for hundred of cdc staff to be laid off jury selection taking time in randolph csc trial mayor trump president fixates on local crime asphalt and lamppost latest news on fbi searching john boltons home office george mason illegally used race in hiring department of education find george mason illegally used race in hiring department of education find a judge ha ordered alligator alcatraz in florida to wind down operation what happens now world cup draw will be held at washington kennedy center trump say kamala harris will take her day book tour to los angeles california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk newsoms profile soar with trump redistricting fight california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk lake lynn answer ferc question raise possibility of entry fee at cheat lake park people officially became u citizen at the new york state fair funeral home owner who stashed nearly decaying body set to be sentenced new york city to get federal police for crime crackdown after dc chicago trump trump praise missouri republican for considering redistricting bolton investigated over classified document not politics vp vance tell nbc community patrol confronts ice officer at city height elementary school parking lot stitt take aim at tulsa mayor decision to prosecute crime in tribal court trump tariff will reduce deficit by trillion over next decade say cbo report ask rusty how do i apply for s and receive my payment trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline uk diplomat receives warning over illegal fishing with jd vance mit global collapse warning revisited humanity enters makeorbreak decade chicago is up next for the national guard theyre screaming for u say trump san carlos and the lastminute commissioner item henderson accepting application for addition to veteran memorial wall trump reacts to canada reversing retaliatory tariff take question at white house erik and lyle menendez can still walk free from prison even if both brother have parole denied a family fight back desantis fire back after dem decries florida move to ditch lgbt rainbow color from crosswalk in orlando hegseth authorizes national guard to carry gun in washington dc ap technology summarybrief at pm edt trump is astonishingly deluded about putin trump official demand apology from george mason president over diversity the new york time the u air force just underwent a massive stress test of how it would fight a highend war in the pacific uk top diplomat get a warning for illegal fishing with u vice president national guard troop in washington will be armed hegseth matt fleming how assembly democrat came to embrace gerrymandering passing the baton in europe could donald trump really win the nobel peace prize asking eric am i wrong for wanting to back out of mexican vacation now that friend included her son beware of the skeeters and malary asking eric am i wrong for backing out of a trip because a friend son is going an energy transition at the crossroad south korea journey toward resilience the u navy drone effort arent going wellbut neither are china pa budget stall again what will it take to break the cycle of delay carney say he will travel to germany next week to deepen tie canada go learn some english customer berates georgian nyc cafe owner now everyones coming to her defense teaching just the fact is not an answer to indoctrination gavin newsoms redistricting gambit a presidential audition not a policy plan fifa world cup draw to take place at kennedy center trump announces tension flare a texas house panel hears a bathroom bill for first time in eight year trump message to dc criminal democrat dont mess with me how some apps are working to solve the epidemic of loneliness what to expect from the ussouth korea summit planned parenthood sue south carolina over medicaid ban certain local voice oppose gov newsoms redistricting campaign cracker barrel new logo sucksand not because of wokeness you idiot ct governor directs flag to halfstaff saturday for state employee fatally injured on job trump say hell ask congress for b for dc improvement letter taxpayer against genocide trump say putin may attend north america world cup it so on after heated back and forth with chris rufo on conservatism jonah goldberg agrees to debate homeowner oppose plan for fencing dune on hollywood beach here why trump say putin may attend north america world cup california ab stall in senate amid parental right opposition trump say putin may attend north america world cup trump say putin may attend north america world cup california governor signed a redistricting plan what happens next trump show off photo putin mailed him from alaska summit but president warns i better be very happy with peace talk after russia ukraine attack policy review committee recap august james jim mcgregor trump say chicago is next for dcstyle federal law enforcement operation a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now shiba inu shib is taking longer than expected to reach new high in pepe coin pepe and this coin to outperform it investing in ozak ai ethereumbased ai token during it under presale could lead to millionaire status by a btc and eth hit ath cadence bank ha million stock holding in texas instrument incorporated txn jpmorgan chase co jpm share sold by rbo co llc hoka ha shoe on sale for a low a right now including bondi and clifton trump administration halt construction of revolution wind farm off mass citing national security new brewery tap into corydons dora ordinance excitement british columbia investment management corp sell share of alphabet inc goog british columbia investment management corp raise holding in broadcom inc avgo air canada say more passenger eligible for reimbursement if flight were cancelled canada grab these safe djia dividend bargain after index hit alltime high nextgen pick best cryptos to buy today a arctic pablos cex listing driving maximum gain potential twothirds of river trash is plastic research fastfood chain lock in meal to fight inflation in newsguild see organizing surge a medium worker fuel grassroots militancy tech ceo urge dignity for billion shift worker amid automation lowes target pro with total home strategy amid sale dip and inflation european postal service halt u shipment over trump tariff china stock surge defies weak economy raising fear of another bust analyst waste management inc nysewm announces quarterly dividend evans city council approves ballot language for permanent road tax bet bonus code orl bonus for seahawks v packer raider v cardinal solana whale rotate capital into layer brett analyst say it could deliver x gain by next year whale are choosing this meme coin a the best crypto to buy in instead of dogecoin doge and shiba sol strengthens on institutional demand xrp jump after whale action and blockdags forecast draw buyer in phoenix wealth advisor sell share of air product and chemical inc apd btc climbed to of global money before fed chair signaled rate cut cointelegraph heritage wealth partner llc buy share of meta platform inc meta palantir technology nasdaqpltr insider ryan taylor sell share palantir technology nasdaqpltr insider ryan taylor sell share of stock promising retail stock to keep an eye on august th jpmorgan chase co jpm is biondo investment advisor llcs th largest position immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say trump appeal in fraud case likely despite his total victory trump appeal in fraud case likely despite his total victory baby boomer turned meme stock trading into a thrilling hobby calling it absolutely gambling trump appeal in fraud case likely despite his total victory this weatherproof storage shed is only during wayfairs labor day blowout sale bank of america nysebac hit new month high whats next invesco qqq qqq share purchased by haverford trust co cardano price prediction ada eye new high yet this lowcap coin ha x more upside beltway buzz august apg asset management nv acquires share of intuitive surgical inc isrg pfizer inc pfe share sold by apg asset management nv what to know about visa for foreign trucker and the politics of a deadly florida crash the best amazon deal to shop right now save up to trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete bitcoin btc price could retrace before a run toward kk but ripple xrp and this coin are aiming high in cryptos next top altcoin why this crypto could shine a xrp fall below best gift for digital artist in trump halt work on nearly complete new england offshore wind project waste management inc wm share acquired by groupe la francaise union pacific corporation unp share purchased by kestra advisory service llc haverford trust co sell share of unitedhealth group incorporated unh waste management inc wm share sold by van hulzen asset management llc groupe la francaise purchase share of walmart inc wmt phoenix wealth advisor trim position in cisco system inc csco bahl gaynor inc increase stake in taiwan semiconductor manufacturing company ltd tsm best of the best bahl gaynor inc sell share of mcdonalds corporation mcd chicago a mess trump vow national guard crackdown layer brett dubbed pepe after early momentum outpaces early doge and shib launch hooter bankruptcy prompt rebrand to tacky familyfriendly are home depot cheapest tool set worth buying here what user say trump halt work on new england offshore wind project thats nearly complete douglas winthrop advisor llc sell share of pepsico inc pep caitlin john llc ha holding in invesco qqq qqq british columbia investment management corp buy share of procter gamble company the pg penticton council willing to work with art gallery after layoff announced penticton get your own steam locomotive how family can save money this backtoschool season northwest minnesota foundation issue over million in grant loan during th quarter why the iea reinstated it business a usual scenario business accelerator academy start in september how u of a help build worldclass entrepreneur dogecoin price target in september but analyst say x gain belong to new lowcaps can solana reach by or is there a better crypto to buy now blockdags m presale and referral reward shift focus from xrp rally and eth market issue trump halt work on new england offshore wind project thats nearly complete yahoocom trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete ai bubble fear spark tech stock slide crash warning rise how and where to bet mlb player prop pick odds for aug garrett crochet among best bet smartleaf asset management llc ha million stock holding in mastercard incorporated ma walmart nysewmt issue fy earnings guidance biondo investment advisor llc ha million stake in unitedhealth group incorporated unh cadence bank sell share of american express company axp forest avenue capital management lp boost holding in vistra corp vst european post suspend u delivery over trumpera tariff biondo investment advisor llc acquires share of amgen inc amgn svb wealth llc lower stock position in blackrock blk svb wealth llc sell share of air product and chemical inc apd air product and chemical inc apd share sold by british columbia investment management corp svb wealth llc sell share of air product and chemical inc apd lionshead wealth management llc ha holding in illinois tool work inc itw biondo investment advisor llc increase stock holding in duke energy corporation duk kruse out a dia director in latest pentagon shakeup cringe watch zohran mamdani plan nyc scavenger hunt is there a prize if youre mugged on the subway cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened u justice department release transcript of interview with ghislaine maxwell kilmar abrego garcia is freed from tennessee jail so he can rejoin family in maryland to await trial greene issue scathing rebuke of condition in gaza i will not be silent about it israel vow to open gate of hell on gaza in chilling warning a famine grip the region u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case kevin oleary sound alarm on rich kid upbringing they become lost in a sea of mediocrity it a disaster for them former dhs official signal he could be next after bolton fbi raid we expect it the lioness at the center of a city hall battered by scandal dnc vote on israel arm embargo may set democratic party course on palestine trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it u seek to deport abrego garcia to uganda hampton county law enforcement to ramp up duo patrol trump administration considering deporting kilmar abrego garcia to uganda his lawyer say secretariat jockey mourned in maine a well a canada dunkin customer warns to check receipt after spotting wellness fee national guard roll out in state not linked to trump crime crackdown wh say the redistricting war between texas and california is about to jolt the midterm politico asking eric were no longer invited to shared family holiday meal what should we do about upcoming wedding redistricting war poised to explode a california and texas make their move la consequential karen bass earns epic ratio over claim city recovery is fastest in state history the redistricting war between texas and california is about to jolt the midterm texas abbott promise quick signature of redistricting plan following overnight senate vote ghislaine maxwell absolves trump and everyone else in doj interview conservative activist slam cracker barrel a company left reeling after logo redesign south korea japan agree to boost tie a challenge mount kilmar abrego garcia released from ice custody after return from el salvador truck driver in crash at center of trump administration feud with newsom is denied bond when trying to explain low dem party polling look no further than awesome duo of newsom and swalwell immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case trump look to chicago next in federal crackdown the wall street journal giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell university of oregon concludes law review discriminated based on perceived national origin against israeli author trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress how redistricting is done and why it could give party an edge in election how redistricting is done and why it could give party an edge in election democrat mock jd vance for having cardboard charisma a he push unpopular budget bill opinion it time for mayo pete buttigieg to find some seasoning what happened to ambition for bay restoration guest commentary kilmar abrego garcia threatened with deportation to uganda larimer county restaurant inspection made aug kilmar abrego garcia threatened with deportation to uganda kilmar abrego garcia threatened with deportation to uganda judge block trump from cutting funding from city and county including denver over sanctuary policy internet tax freedom act preempt new york imposition of tax fbi target john boltons home and office trump he not a smart guy but he could be a very unpatriotic guy inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal rachel bitecofer warns that bolton is just the start and trump will go after the rest of u inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal what we know about china and russia new strategic bomber inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal zelenskyy say security guarantee for ukraine to be ready soon bill maher applauds gavin newsom for mocking donald trump i think it very funny floridarun alligator alcatraz violates u law aclu say russia announces support for venezuela to defend sovereignty amid growing military tension with the united state gianno caldwell mull senate bid a chicagoans are begging for change on crime woe trump threatens chicago with next national guard invasion cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview the owl eye liberty and memory from epstein suicide to trump and clinton takeaway from ghislaine maxwell transcript how can israel engineer a famine in gaza in the st century what we learned from the ghislaine maxwell doj interview texas gov abbott say hell swiftly sign redistricting map after lawmaker approve them jeff bezos said he would have felt icky had he taken any more share of amazon i just didnt feel good smart money strategy what the pro buy when the crypto market crash radioactive shrimp update walmart store brand and other brand recalled european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff a winning powerball ticket ha been sold in western new york the sp hasnt yielded this little since the dotcom bubble here what investor can do the motley fool just ranked the biggest financial stock here why the no pick could be your best investment mezcal producer preserve traditional method a demand for liquor grows minute european postal service suspend shipment of package to u over tariff kpop demon hunter give netflix it first boxoffice win curry join the bank holiday sale bonanza with it epic deal event here are the best offer id buy self driving taxi may be coming to nyc a waymo win first av testing permit mashable rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important deadline in security class action fi ice cream sold at walmarts across state recalled due to undeclared allergen here how a gamestop purchase turned into a bitcoin jackpot ice cream sold at walmarts across state recalled due to undeclared allergen fox business prediction lucid group sale will soar over the next year if this happens solar executive warn that trump attack on renewables will lead to power crunch that spike electricity price pueblo county home listing asked for less money in july see the current median price here prediction these trilliondollar artificial intelligence ai stock could strike a megadeal that wall street isnt ready for cold wallet cashback utility and presale pricing create a upside case while chainlink and shiba inu struggle maintenance compliance burden viability of hopi water treatment system ethereum in trouble xrp might breakout buyer turn to blockdag to earn referral reward acting a the executor of a will can be a very lucrative job the last word national guard troop to be force multiplier for ice homan little pepe crypto price prediction is lilpepe a good investment for longterm holder here how much you should aim to invest in the invesco qqq etf to get to million or more by retirement state audit question m in federal spending by moses lake school district blockchain stock worth watching august th owner scale back golden mile shopping center redevelopment rosen global investor counsel encourages easterly rocmuni high income municipal bond fund comerica bank lower stake in alphabet inc goog trump tap airbnb cofounder a st government design head to lead huge web overhaul trump tap airbnb cofounder a st government design head to lead huge web overhaul fox business offgrid living next new real estate trend a application for rural mortgage skyrocket rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before epstein accuser virginia giuffre wrote a memoir month after her death it coming out powell warning signal unemployment claim jump to highest in year cardano price outlook can ada reach trumprelated defi platform world liberty financial debut wlfi token on ethereum mainnet rosen global investor counsel encourages altimmune inc investor to secure counsel before important deadline in security class action alt the best meme coin presale stampede is loading whitelist labubull now or watch it moon without you backtoschool deal tellos unlimited plan get you cell service for per month your first month nexus gold cvenxs stock price up whats next mason resource cvellg stock price up here why mason resource cvellg trading up here what happened national guard troop to be force multiplier for ice homan freedom investment management inc purchase share of procter gamble company the pg ascent group llc raise stock holding in ameri</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9988</v>
+      </c>
+      <c r="O44" t="n">
+        <v>214</v>
+      </c>
+      <c r="P44" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>380</v>
+      </c>
+      <c r="S44" t="n">
+        <v>203</v>
+      </c>
+      <c r="T44" t="n">
+        <v>451</v>
+      </c>
+      <c r="U44" t="n">
+        <v>318</v>
+      </c>
+      <c r="V44" t="n">
+        <v>124</v>
+      </c>
+      <c r="W44" t="n">
+        <v>91</v>
+      </c>
+      <c r="X44" t="n">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X44"/>
+  <dimension ref="A1:X45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,6 +3894,84 @@
         <v>167</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6465.93994140625</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6468.3701171875</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6429.2099609375</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6435.490234375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4867680000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0041339951911349</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>top altcoins to buy now analyst pick with x potential in the next bull run south bay lawmaker new push to keep california highspeed rail project on track blackrock canada announces final august cash distribution for the ishares premium money market etf integral metal announces closing of private placement offering david gardner on rule breaker investing ibd live qa stock list for monday aug elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit modern farmhouse in henderson neighborhood listed for m dust off your keyboard this fall get a powerful canless duster for off can in nuscale power stock turn into by ap sport summarybrief at pm edt top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers smart altcoin investment for august with huge price prediction upside american natural gas demand poised for historic high in if youd invested in oklo stock last year here how much money youd have today medium advisory infrastructure announcement in surrey roches u subsidiary genentech break ground on stateoftheart manufacturing facility in north carolina usa transamerica welcome jason frain a head of retirement solution dogecoin news today doge face critical support at whats next best opensource datasets for your next project canadian u official are to meet after canada remove some tariff protecting main street money strengthening mississippi bank sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach misuta chow to close after year top venture capital crms to elevate your investment strategy in new tec open new worthington showroom clark county resident with bad credit on the rise joint development district could generate income for perrysburg township ohio millionaire politician a stunning wealth gap between u and our representative bank and sole proprietor three bill would protect california worker from ai management but will cost stand in the way sevenyear car loan are becoming normal a car price stay high white castle charge diner jawdropping for combo a store make annoying drivethru change bunch of jerk research show how brand can benefit from reclaiming insult where you are and where youve been food industry lobby for tariff exemption on seafood fresh produce a it warns price could spike tariff bingo is tough texas manufacturer sweat trump tariff high interest rate cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price watch cracker barrel face backlash over rebranding car are so expensive that buyer need year loan court denies beverage company preliminary injunction in trade secret case citing conflicting evidence tesla could fall tomorrow and i wouldnt buy a share say top fund manager blizzard cofounder game startup dreamhaven struggle amid industry glut july newhome sale top expectation emini sp rally test gann and fibonacci resistance into august cycle crest southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat levi korsinsky reminds shareholder of a lead plaintiff deadline of september in lineage inc lawsuit line intel say trump plan for u stake in company pose business risk the washington post best gaming mouse with side button to buy in kaldvik a kldvk q webcast result august at cet why zeroclick search is forcing business to pivot how to implement your oem maintenance schedule into your eld so you never miss a critical interval netflixs kpop demon hunter top box office despite fewer screen shorter run rep thomas h kean jr liberty broadband corporation nasdaqlbrdk share rep ritchie torres sell equity lifestyle property inc nyseels share arista network nyseanet stock acquired sen angus s king jr bank of america nysebac share acquired sen angus s king jr pepsico nasdaqpep share unloaded rep ritchie torres equity residential nyseeqr stock unloaded rep ritchie torres rep ritchie torres sell are management corporation nyseares stock sen angus s king jr purchase share of on holding ag nyseonon rep ritchie torres sell colgatepalmolive company nysecl share eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of lowes company inc nyselow life without most of the fcpa six month in gas price back up gas pice back up european carrier pause some shipment to u a they prepare for end of de minimis exemption city of charlotte to give out free air conditioning unit we now know which crime are aok with beloved socialist candidate zohran mamdani for now wild video show mountain lion walking right through family front door in california stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally los angeles area unemployment claim surged following january wildfire report walmart fire vp over kickback lay off hb worker little pepe lilpepe shine a best meme coin for attracting dogecoin doge holder with prospect this quest diagnostics analyst is no longer bullish here are top downgrade for monday tech ipo darling give up some gain tharimmune thar stock is surging monday whats going on usdchf hit new high a usd strengthens eye further gain ahead eurusd reach target tezos is leveling the playing field giving everyone access to uranium the commodity powering the energy of the future tokenized equity in the crosshairs of global stock exchange what happened elon musk xai drop public benefit status echoing openai shift trump want to prosecute flag burner the supreme court ha already said thats illegal dont mourn the death of palestinian journalist talkin bout a revolution greenwood cemetery commemorates the battle of brooklyn fema worker warn agency at risk of hurricane katrinatype failure cnn politics trump say he could rename department of defense to department of war soon trump say he could rename department of defense to department of war soon trump want to meet north korea kim this year he tell south korea trump get a ridiculous badge for turning dc into a police state the alliance of authoritarianism and oligarchy show it hand in dc flower the tiresome tale of amanda knox campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger university of florida pick an interim president after last choice wa rejected university of florida pick an interim president after last choice wa rejected trump hegseth float renaming defense department to department of war trump hegseth float renaming defense department to department of war military time kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort intels role in the uschina chip war analysis trump tortured history of legally targeting his foe cnn politics alleged retaliation by high school coach against athlete lead to first amendment claim house republican seek review of dc crime data dems issue threat of maryland governor redrawing congressional map yeah about that trump executive order prohibiting flag burning is unconstitutional trump predicts conclusive ending to gaza war within three week prior lake teacher lawsuit claim district violated her free speech right over deportation social post venezuela release political prisoner a u ramp up pressure with naval armada theyre going to be brought down trump vow to go after bidens adviser theyre going to be brought down trump vow to go after bidens adviser israel express regret after outcry over hospital strike city pass controversial ordinance targeting homeless activity equity research analyst price target change for august th abo ahh amgn apld avgo bj bke cbre cogt coty editorial jail commissary fund in the spotlight trump say nbc abc should lose license over news coverage richard grenell politely make katie couric look like the intolerant hag she really is and it glorious trump threatens nbc and abc here why he cant revoke their license trump meet south korean president industrial leader in washington sen angus s king jr buy alphabet inc nasdaqgoogl stock rep ritchie torres sell are management corporation nyseares stock sen angus s king jr sell thermo fisher scientific inc nysetmo stock kinder morgan nysekmi share unloaded rep ritchie torres rep ritchie torres sell off share of cocacola company the nyseko rep ritchie torres sell qualcomm incorporated nasdaqqcom stock eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of blackstone inc nysebx denton isds communication of student stabbing criticized by parent exmaga rep dish out advice on crybaby trump after social medium rant south park escalates it war against trump in a brutal episode donna brazile dismisses gavin newsoms trump trolling on social medium say these are serious time the hidden crisis of black land loss in the wake of slavery the excerpt west virginia national guard troop in dc now authorized to carry weapon trump say he would like to have another meeting with kim jong un trump sign order cracking down on cashless bail slapping federal charge on dc suspect philadelphia mass transit cut foreshadow possible similar move by other agency across u the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit ohio sued over proofofcitizenship rule for voter registration robert f kennedy jr back morrisey on west virginia school vaccine exemption who cashing in on trump immigration crackdown it not the american people nor the federal or state government democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james trump battle with u senate judiciary grassley over homestate pick for judge a federal grant termination grow award recipient should be proactive but also preserve their right trump sign executive order directing doj to prosecute flag burning julio cesar chavez jr released from mexican maximumsecurity prison ahead of trial for alleged cartel tie face the nation no threat to the public situation on catawba river in belmont end peacefully epstein accuser to release unsparing memoir with disturbing detail axios trump dc takeover is a modern day rebirth of a nation hundred from across pa protest in philipsburg against the moshannon valley processing center gillette senator accuses city council of violating the public trust on nuclear issue trump sign order aimed at ending cashless bail policy opening date announced for controversial overnight homeless shelter in portland pearl district bridge cost historical marker on agenda for rome common council chief of war episode recap sled dead redemption asking eric i meant no harm by the compliment i paid a friend california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis trump threatens lawsuit over centuryold senate tradition delaying his nominee hispanic tiktoker arrested by ice in los angeles during live stream democratic national committee kick off summer meeting kansa house speaker want to slash million from state budget target medicaid for cut some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent let meet salvadoran man in trump immigration row to be deported to uganda official salvadoran man in trump immigration row to be deported to uganda official</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>top altcoins to buy now analyst pick with x potential in the next bull run south bay lawmaker new push to keep california highspeed rail project on track blackrock canada announces final august cash distribution for the ishares premium money market etf integral metal announces closing of private placement offering david gardner on rule breaker investing ibd live qa stock list for monday aug elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit modern farmhouse in henderson neighborhood listed for m dust off your keyboard this fall get a powerful canless duster for off can in nuscale power stock turn into by ap sport summarybrief at pm edt top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers smart altcoin investment for august with huge price prediction upside american natural gas demand poised for historic high in if youd invested in oklo stock last year here how much money youd have today medium advisory infrastructure announcement in surrey roches u subsidiary genentech break ground on stateoftheart manufacturing facility in north carolina usa transamerica welcome jason frain a head of retirement solution dogecoin news today doge face critical support at whats next best opensource datasets for your next project canadian u official are to meet after canada remove some tariff protecting main street money strengthening mississippi bank sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach misuta chow to close after year top venture capital crms to elevate your investment strategy in new tec open new worthington showroom clark county resident with bad credit on the rise joint development district could generate income for perrysburg township ohio millionaire politician a stunning wealth gap between u and our representative bank and sole proprietor three bill would protect california worker from ai management but will cost stand in the way sevenyear car loan are becoming normal a car price stay high white castle charge diner jawdropping for combo a store make annoying drivethru change bunch of jerk research show how brand can benefit from reclaiming insult where you are and where youve been food industry lobby for tariff exemption on seafood fresh produce a it warns price could spike tariff bingo is tough texas manufacturer sweat trump tariff high interest rate cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price watch cracker barrel face backlash over rebranding car are so expensive that buyer need year loan court denies beverage company preliminary injunction in trade secret case citing conflicting evidence tesla could fall tomorrow and i wouldnt buy a share say top fund manager blizzard cofounder game startup dreamhaven struggle amid industry glut july newhome sale top expectation emini sp rally test gann and fibonacci resistance into august cycle crest southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat levi korsinsky reminds shareholder of a lead plaintiff deadline of september in lineage inc lawsuit line intel say trump plan for u stake in company pose business risk the washington post best gaming mouse with side button to buy in kaldvik a kldvk q webcast result august at cet why zeroclick search is forcing business to pivot how to implement your oem maintenance schedule into your eld so you never miss a critical interval netflixs kpop demon hunter top box office despite fewer screen shorter run rep thomas h kean jr liberty broadband corporation nasdaqlbrdk share rep ritchie torres sell equity lifestyle property inc nyseels share arista network nyseanet stock acquired sen angus s king jr bank of america nysebac share acquired sen angus s king jr pepsico nasdaqpep share unloaded rep ritchie torres equity residential nyseeqr stock unloaded rep ritchie torres rep ritchie torres sell are management corporation nyseares stock sen angus s king jr purchase share of on holding ag nyseonon rep ritchie torres sell colgatepalmolive company nysecl share eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of lowes company inc nyselow life without most of the fcpa six month in gas price back up gas pice back up european carrier pause some shipment to u a they prepare for end of de minimis exemption city of charlotte to give out free air conditioning unit we now know which crime are aok with beloved socialist candidate zohran mamdani for now wild video show mountain lion walking right through family front door in california stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally los angeles area unemployment claim surged following january wildfire report walmart fire vp over kickback lay off hb worker little pepe lilpepe shine a best meme coin for attracting dogecoin doge holder with prospect this quest diagnostics analyst is no longer bullish here are top downgrade for monday tech ipo darling give up some gain tharimmune thar stock is surging monday whats going on usdchf hit new high a usd strengthens eye further gain ahead eurusd reach target tezos is leveling the playing field giving everyone access to uranium the commodity powering the energy of the future tokenized equity in the crosshairs of global stock exchange what happened elon musk xai drop public benefit status echoing openai shift trump want to prosecute flag burner the supreme court ha already said thats illegal dont mourn the death of palestinian journalist talkin bout a revolution greenwood cemetery commemorates the battle of brooklyn fema worker warn agency at risk of hurricane katrinatype failure cnn politics trump say he could rename department of defense to department of war soon trump say he could rename department of defense to department of war soon trump want to meet north korea kim this year he tell south korea trump get a ridiculous badge for turning dc into a police state the alliance of authoritarianism and oligarchy show it hand in dc flower the tiresome tale of amanda knox campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger university of florida pick an interim president after last choice wa rejected university of florida pick an interim president after last choice wa rejected trump hegseth float renaming defense department to department of war trump hegseth float renaming defense department to department of war military time kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort intels role in the uschina chip war analysis trump tortured history of legally targeting his foe cnn politics alleged retaliation by high school coach against athlete lead to first amendment claim house republican seek review of dc crime data dems issue threat of maryland governor redrawing congressional map yeah about that trump executive order prohibiting flag burning is unconstitutional trump predicts conclusive ending to gaza war within three week prior lake teacher lawsuit claim district violated her free speech right over deportation social post venezuela release political prisoner a u ramp up pressure with naval armada theyre going to be brought down trump vow to go after bidens adviser theyre going to be brought down trump vow to go after bidens adviser israel express regret after outcry over hospital strike city pass controversial ordinance targeting homeless activity equity research analyst price target change for august th abo ahh amgn apld avgo bj bke cbre cogt coty editorial jail commissary fund in the spotlight trump say nbc abc should lose license over news coverage richard grenell politely make katie couric look like the intolerant hag she really is and it glorious trump threatens nbc and abc here why he cant revoke their license trump meet south korean president industrial leader in washington sen angus s king jr buy alphabet inc nasdaqgoogl stock rep ritchie torres sell are management corporation nyseares stock sen angus s king jr sell thermo fisher scientific inc nysetmo stock kinder morgan nysekmi share unloaded rep ritchie torres rep ritchie torres sell off share of cocacola company the nyseko rep ritchie torres sell qualcomm incorporated nasdaqqcom stock eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of blackstone inc nysebx denton isds communication of student stabbing criticized by parent exmaga rep dish out advice on crybaby trump after social medium rant south park escalates it war against trump in a brutal episode donna brazile dismisses gavin newsoms trump trolling on social medium say these are serious time the hidden crisis of black land loss in the wake of slavery the excerpt west virginia national guard troop in dc now authorized to carry weapon trump say he would like to have another meeting with kim jong un trump sign order cracking down on cashless bail slapping federal charge on dc suspect philadelphia mass transit cut foreshadow possible similar move by other agency across u the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit ohio sued over proofofcitizenship rule for voter registration robert f kennedy jr back morrisey on west virginia school vaccine exemption who cashing in on trump immigration crackdown it not the american people nor the federal or state government democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james trump battle with u senate judiciary grassley over homestate pick for judge a federal grant termination grow award recipient should be proactive but also preserve their right trump sign executive order directing doj to prosecute flag burning julio cesar chavez jr released from mexican maximumsecurity prison ahead of trial for alleged cartel tie face the nation no threat to the public situation on catawba river in belmont end peacefully epstein accuser to release unsparing memoir with disturbing detail axios trump dc takeover is a modern day rebirth of a nation hundred from across pa protest in philipsburg against the moshannon valley processing center gillette senator accuses city council of violating the public trust on nuclear issue trump sign order aimed at ending cashless bail policy opening date announced for controversial overnight homeless shelter in portland pearl district bridge cost historical marker on agenda for rome common council chief of war episode recap sled dead redemption asking eric i meant no harm by the compliment i paid a friend california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis trump threatens lawsuit over centuryold senate tradition delaying his nominee hispanic tiktoker arrested by ice in los angeles during live stream democratic national committee kick off summer meeting kansa house speaker want to slash million from state budget target medicaid for cut some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent let meet salvadoran man in trump immigration row to be deported to uganda official salvadoran man in trump immigration row to be deported to uganda official</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.9994</v>
+      </c>
+      <c r="O45" t="n">
+        <v>95</v>
+      </c>
+      <c r="P45" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>126</v>
+      </c>
+      <c r="S45" t="n">
+        <v>69</v>
+      </c>
+      <c r="T45" t="n">
+        <v>166</v>
+      </c>
+      <c r="U45" t="n">
+        <v>139</v>
+      </c>
+      <c r="V45" t="n">
+        <v>52</v>
+      </c>
+      <c r="W45" t="n">
+        <v>41</v>
+      </c>
+      <c r="X45" t="n">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X45"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3972,6 +3972,84 @@
         <v>35</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6481.39990234375</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6487.06005859375</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6457.83984375</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6462.259765625</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4143680000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0023909843081744</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>british american tobacco cfo step down abruptly hostess ding dong pulled over mold concern trump cant fire jerome powell so he going after the rest of the fed poverty in mass it about race and place the republican editorial democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island portland mercury owner buy the chicago reader new era unlocked taylor swift and travis kelce announce engagement how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in extended comment period for benson aluminum recycling plant xrp news today xrp face resistance a whale activity and xrp card boost sentiment zenith netzero gain scc accreditation a iso validation and verification body public hearing slated on draft ny energy plan daniel luries family zoning plan is anything but crypto investor eye lyno ai for s biggest roi opportunity meme coin that will turn into faster than dogecoin doge can soar x and shiba inu shib x saudi arabia and india top the list of russia fuel oil buyer alibaba debut avatar update to it video ai model why the u government is not the savior intel need ethereum price uniswap latest news aave staking option remittix announces major cex listing keanetech maple bitflow why maple bitflow trading platform is being touted a a gamechanger by industry insider read canada trading report justice alito report no gift trip and an active stock portfolio st louis man sentenced to year for seconddegree murder at dutchtown gas station new report these are the most popular potato chip brand in each state courtney panik redefines hr for corporate transformation ai race redefines productivity palantir may squeeze short study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death icu urge cm to update ceus reimbursement citing clinical benefit for patient and healthcare system jack smith legal team fire back against ethic complaint the new york time official opening of phase iii of villa forestville more social and affordable housing unit for senior in forestville peter friedlander departing netflix jinny howe upped to head of u canada scripted series economist warns agi in year could drive wage to zero push ubi trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule how corporate gifting can enhance every employee milestone mortgage fraud claim give trump weapon against lisa cook and others edward jones begin layoff including at it headquarters stock market today dow waver after trump move to oust fed governor cook live update the wall street journal donald trump say he want to rebrand his big beautiful bill nbc news vra investor news if you have suffered loss in vera bradley inc nasdaq vra you are embattled fed gov lisa cook say shell sue trump to keep her job new gallup poll show point swing in trump approval rating man arrested after car chase end in crash into wake forest reservoir beam global score major win a u government extends procurement contract kroger shuts door on location for good with more closure on the chopping block after ceo reveals chain future u challenge foreign digital tax with tariff on tech giant dow jones payment giant american express tesla stock in or near buy zone budget cut will hurt west virginia powerball jackpot reach m seventh largest prize in game history stream realty partner triple miami footprint amid rapid florida growth rosen a leading law firm encourages xplr infrastructure lp fka nextera energy partner lp investor to secure counsel before important deadline in security class action xifr nep crypto news today robinhood microstrategy miss sp kraken meet sec trump medium land b deal ion grove rosen a leading law firm encourages snap inc investor to secure counsel before important residential real estate expert nicole curcio share why home are selling fast in hellonation slqt investor have opportunity to lead selectquote inc security fraud lawsuit rosen a leading law firm encourages snap inc investor to secure counsel before important deadline in security class action snap magnolia isd approves m balanced budget including teacher pay raise marketing a lastminute concern a cvcc bond vote loom agristo potato processing project progress in grand fork where american earn six figure without a degree study numerai secures up to m commitment from jpmorgan asset management biggest layoff of are we expecting more huntington beloved restaurant is closing after year on september eli lilly lly prepares for weight loss pill approval after latestage clinical trial tipranks cd v highyield saving account which earns more interest now slqt investor have opportunity to lead selectquote inc security fraud lawsuit bmo unveils plan to invest in it u branch technology a u tariff exemption for small order end friday it a big deal to some shopper and business how to regretproof your home purchase messer partner with u titanium producer to support aerospace growth trk enterprise inc expands market reach with acquisition of summit laydown service inc katy isd adopts b budget despite projected m shortfall for fy niagara tourism spending soar to billion in boosting local economy fed barkin his forecast is for a modest cut in interest rate trump is out to end the fed autonomy here how he trying to get his way arvore declares it july distribution annualized trump tell cracker barrel to ditch it new logo after maga meltdown furniture seller could face additional white house tariff inspirit iot japanese power plant turn saltwater into electricityand it a glimpse into the future walmart slashed off this blackstone burner griddle and itll still deliver before labor day zillow and berkshire hathaway homeservices team up to empower agent supercharge listing using showcase fcp acquires unit district west gable apartment in west miami fl how democrat plan to use federal medicaid cut in midterm messaging why lululemons global expansion could outweigh north america slowdown wichita city council approves budget with first property tax rate cut in decade trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation white house accuses pritzker illinois dems of whining while chicago crime rage embattled fed gov lisa cook say shell sue trump to keep her job business why the advancement of religion a a charitable purpose must be preserved in canada thursday is next opportunity to meet with santa fe mayor haros charged with murder of son monthold emmanuel in riverside county la could see more border patrol agent soon sector chief say conrad black to hold canada together ottawa need a daring strategy milwaukee judge must face charge after motion to dismiss denied israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet hakeem jeffries ripped for noting lisa cook race while slamming trump for trying to fire her who give a flying fruitcake what color she is trump dc crime crackdown could revive death penalty for convicted murderer jack smith legal team fire back against ethic complaint the new york time butler county sheriff within legal right to hold ice detainee civilly ohio ag opinion say yearold democrat make way for rising farleft star after republican got their way with redistricting opinion celeb chef blast confused trump for restaurant claim embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job trump call for death penalty for anyone charged with killing someone in washington dc cook firing take the fed into the unknown democratic party scrap resolution on israel and gaza after fraught debate democratic party scrap resolution on israel and gaza after fraught debate the new york time orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin dr congo m rebel resume talk in qatar after renewed violence in east court toss trump lawsuit against maryland judge over u deportation ukrainian woman who fled war stabbed to death at charlotte light rail station democrat latest move on the gaza war spark backlash and backtracking democrat latest move on the gaza war spark backlash and backtracking north myrtle beach election filing period is open here who filed so far cracker barrel cave old country store to bring back old logo after blowback what to know about lisa cook the fed governor who trump say he firing trump team floated energy incentive with russia in sideline ukraine peace talk report five question and expert answer about where the ussouth korea alliance go from here trump asks ntd white house correspondent to share her dc mugging story at cabinet meeting west hartford state legislator join the crowd looking to replace rep john larson taiwan deports japanese man after filming prochina video in taipei the foreigner working for doge politico the foreigner working for doge u envoy israel counterproposal to lebanon disarmament plan coming arizona department of education apologizes to esa parent after some personally identifiable information wa given to local medium including news trump announces name change for department of defense too defensive trump dot threatens to withhold fund from state that dont enforce english requirement for truck driver nbc news bc green party candidate stopping in armstrong for meet and greet trump appointee call out trump administration effort to smear judge court reject trump doj lawsuit against maryland judge detroit school urge judge to halt chickfila construction next door u envoy tell arab journalist in lebanon to be civilised utah ordered to redraw congressional map opening up possible democratic seat video kilmar abrego garcia take word shot at the united state a he escorted through ice facility utah ordered to redraw congressional map opening up possible democratic seat utah ordered to redraw congressional map seat for democrat possible cbs news adam sandler questioned over snl song calling out antisemitic musician trump push to fire fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation utah judge strike down republican congressional map in gerrymandering case house oversight committee subpoena epstein estate seeking alleged trump note is trump doing a better or worse job than biden here what a new poll found whistleblower say trump official copied million of social security number hhs asks state and territory to remove gender ideology content from sex ed material social security refusing to make payment change after inconvenient law and issue wont be fixed for month exclusive gop chairman think his party ha what it take to beat the purple out of georgia duffy threatens state that dont enforce english language requirement for truck driver duffy threatens state that dont enforce english language requirement for truck driver let talk knoxville back to school police chief aaron fuller he wa shot and killed by a border patrol agent year ago his family still demand justice roadway crack sealing work scheduled to begin wednesday with book and kid in tow this boyle height mom is fighting for her community library she pushed to overturn trump loss in the election now shell help oversee u election security propublica the bb lancer just finished another btf mission can gavin newsoms bold move save the democrat and win in robert f wrobel wisconsin democrat propose new funding for knowlesnelson stewardship grand fork district republican party ready for day window to select state house replacement pa top court official facebook post subject to same righttoknow standard a other record she pushed to overturn trump loss in the election now shell help oversee u election security john bolton mock trump nobel peace obsession in first comment since fbi raid meta to spend ten of million on proai super pac indigenous youth make historic ride down the klamath river lula denounces u decision to revoke visa from brazilian justice minister</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>british american tobacco cfo step down abruptly hostess ding dong pulled over mold concern trump cant fire jerome powell so he going after the rest of the fed poverty in mass it about race and place the republican editorial democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island portland mercury owner buy the chicago reader new era unlocked taylor swift and travis kelce announce engagement how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in extended comment period for benson aluminum recycling plant xrp news today xrp face resistance a whale activity and xrp card boost sentiment zenith netzero gain scc accreditation a iso validation and verification body public hearing slated on draft ny energy plan daniel luries family zoning plan is anything but crypto investor eye lyno ai for s biggest roi opportunity meme coin that will turn into faster than dogecoin doge can soar x and shiba inu shib x saudi arabia and india top the list of russia fuel oil buyer alibaba debut avatar update to it video ai model why the u government is not the savior intel need ethereum price uniswap latest news aave staking option remittix announces major cex listing keanetech maple bitflow why maple bitflow trading platform is being touted a a gamechanger by industry insider read canada trading report justice alito report no gift trip and an active stock portfolio st louis man sentenced to year for seconddegree murder at dutchtown gas station new report these are the most popular potato chip brand in each state courtney panik redefines hr for corporate transformation ai race redefines productivity palantir may squeeze short study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death icu urge cm to update ceus reimbursement citing clinical benefit for patient and healthcare system jack smith legal team fire back against ethic complaint the new york time official opening of phase iii of villa forestville more social and affordable housing unit for senior in forestville peter friedlander departing netflix jinny howe upped to head of u canada scripted series economist warns agi in year could drive wage to zero push ubi trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule how corporate gifting can enhance every employee milestone mortgage fraud claim give trump weapon against lisa cook and others edward jones begin layoff including at it headquarters stock market today dow waver after trump move to oust fed governor cook live update the wall street journal donald trump say he want to rebrand his big beautiful bill nbc news vra investor news if you have suffered loss in vera bradley inc nasdaq vra you are embattled fed gov lisa cook say shell sue trump to keep her job new gallup poll show point swing in trump approval rating man arrested after car chase end in crash into wake forest reservoir beam global score major win a u government extends procurement contract kroger shuts door on location for good with more closure on the chopping block after ceo reveals chain future u challenge foreign digital tax with tariff on tech giant dow jones payment giant american express tesla stock in or near buy zone budget cut will hurt west virginia powerball jackpot reach m seventh largest prize in game history stream realty partner triple miami footprint amid rapid florida growth rosen a leading law firm encourages xplr infrastructure lp fka nextera energy partner lp investor to secure counsel before important deadline in security class action xifr nep crypto news today robinhood microstrategy miss sp kraken meet sec trump medium land b deal ion grove rosen a leading law firm encourages snap inc investor to secure counsel before important residential real estate expert nicole curcio share why home are selling fast in hellonation slqt investor have opportunity to lead selectquote inc security fraud lawsuit rosen a leading law firm encourages snap inc investor to secure counsel before important deadline in security class action snap magnolia isd approves m balanced budget including teacher pay raise marketing a lastminute concern a cvcc bond vote loom agristo potato processing project progress in grand fork where american earn six figure without a degree study numerai secures up to m commitment from jpmorgan asset management biggest layoff of are we expecting more huntington beloved restaurant is closing after year on september eli lilly lly prepares for weight loss pill approval after latestage clinical trial tipranks cd v highyield saving account which earns more interest now slqt investor have opportunity to lead selectquote inc security fraud lawsuit bmo unveils plan to invest in it u branch technology a u tariff exemption for small order end friday it a big deal to some shopper and business how to regretproof your home purchase messer partner with u titanium producer to support aerospace growth trk enterprise inc expands market reach with acquisition of summit laydown service inc katy isd adopts b budget despite projected m shortfall for fy niagara tourism spending soar to billion in boosting local economy fed barkin his forecast is for a modest cut in interest rate trump is out to end the fed autonomy here how he trying to get his way arvore declares it july distribution annualized trump tell cracker barrel to ditch it new logo after maga meltdown furniture seller could face additional white house tariff inspirit iot japanese power plant turn saltwater into electricityand it a glimpse into the future walmart slashed off this blackstone burner griddle and itll still deliver before labor day zillow and berkshire hathaway homeservices team up to empower agent supercharge listing using showcase fcp acquires unit district west gable apartment in west miami fl how democrat plan to use federal medicaid cut in midterm messaging why lululemons global expansion could outweigh north america slowdown wichita city council approves budget with first property tax rate cut in decade trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation white house accuses pritzker illinois dems of whining while chicago crime rage embattled fed gov lisa cook say shell sue trump to keep her job business why the advancement of religion a a charitable purpose must be preserved in canada thursday is next opportunity to meet with santa fe mayor haros charged with murder of son monthold emmanuel in riverside county la could see more border patrol agent soon sector chief say conrad black to hold canada together ottawa need a daring strategy milwaukee judge must face charge after motion to dismiss denied israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet hakeem jeffries ripped for noting lisa cook race while slamming trump for trying to fire her who give a flying fruitcake what color she is trump dc crime crackdown could revive death penalty for convicted murderer jack smith legal team fire back against ethic complaint the new york time butler county sheriff within legal right to hold ice detainee civilly ohio ag opinion say yearold democrat make way for rising farleft star after republican got their way with redistricting opinion celeb chef blast confused trump for restaurant claim embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job trump call for death penalty for anyone charged with killing someone in washington dc cook firing take the fed into the unknown democratic party scrap resolution on israel and gaza after fraught debate democratic party scrap resolution on israel and gaza after fraught debate the new york time orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin dr congo m rebel resume talk in qatar after renewed violence in east court toss trump lawsuit against maryland judge over u deportation ukrainian woman who fled war stabbed to death at charlotte light rail station democrat latest move on the gaza war spark backlash and backtracking democrat latest move on the gaza war spark backlash and backtracking north myrtle beach election filing period is open here who filed so far cracker barrel cave old country store to bring back old logo after blowback what to know about lisa cook the fed governor who trump say he firing trump team floated energy incentive with russia in sideline ukraine peace talk report five question and expert answer about where the ussouth korea alliance go from here trump asks ntd white house correspondent to share her dc mugging story at cabinet meeting west hartford state legislator join the crowd looking to replace rep john larson taiwan deports japanese man after filming prochina video in taipei the foreigner working for doge politico the foreigner working for doge u envoy israel counterproposal to lebanon disarmament plan coming arizona department of education apologizes to esa parent after some personally identifiable information wa given to local medium including news trump announces name change for department of defense too defensive trump dot threatens to withhold fund from state that dont enforce english requirement for truck driver nbc news bc green party candidate stopping in armstrong for meet and greet trump appointee call out trump administration effort to smear judge court reject trump doj lawsuit against maryland judge detroit school urge judge to halt chickfila construction next door u envoy tell arab journalist in lebanon to be civilised utah ordered to redraw congressional map opening up possible democratic seat video kilmar abrego garcia take word shot at the united state a he escorted through ice facility utah ordered to redraw congressional map opening up possible democratic seat utah ordered to redraw congressional map seat for democrat possible cbs news adam sandler questioned over snl song calling out antisemitic musician trump push to fire fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation utah judge strike down republican congressional map in gerrymandering case house oversight committee subpoena epstein estate seeking alleged trump note is trump doing a better or worse job than biden here what a new poll found whistleblower say trump official copied million of social security number hhs asks state and territory to remove gender ideology content from sex ed material social security refusing to make payment change after inconvenient law and issue wont be fixed for month exclusive gop chairman think his party ha what it take to beat the purple out of georgia duffy threatens state that dont enforce english language requirement for truck driver duffy threatens state that dont enforce english language requirement for truck driver let talk knoxville back to school police chief aaron fuller he wa shot and killed by a border patrol agent year ago his family still demand justice roadway crack sealing work scheduled to begin wednesday with book and kid in tow this boyle height mom is fighting for her community library she pushed to overturn trump loss in the election now shell help oversee u election security propublica the bb lancer just finished another btf mission can gavin newsoms bold move save the democrat and win in robert f wrobel wisconsin democrat propose new funding for knowlesnelson stewardship grand fork district republican party ready for day window to select state house replacement pa top court official facebook post subject to same righttoknow standard a other record she pushed to overturn trump loss in the election now shell help oversee u election security john bolton mock trump nobel peace obsession in first comment since fbi raid meta to spend ten of million on proai super pac indigenous youth make historic ride down the klamath river lula denounces u decision to revoke visa from brazilian justice minister</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-0.9806</v>
+      </c>
+      <c r="O46" t="n">
+        <v>114</v>
+      </c>
+      <c r="P46" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>119</v>
+      </c>
+      <c r="S46" t="n">
+        <v>93</v>
+      </c>
+      <c r="T46" t="n">
+        <v>156</v>
+      </c>
+      <c r="U46" t="n">
+        <v>150</v>
+      </c>
+      <c r="V46" t="n">
+        <v>86</v>
+      </c>
+      <c r="W46" t="n">
+        <v>25</v>
+      </c>
+      <c r="X46" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X46"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4050,6 +4050,84 @@
         <v>41</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6501.85986328125</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6508.22998046875</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6466.9599609375</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6483.83984375</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4283760000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0031567194195349</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>silver stabilizes above a mean reversion structure hold ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard fashion model reckon with ai model and digital clone after controversial ad appears in vogue ai profit window is wide open here how to time it from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast safer foundation to host open house at new employment service location in rock island are workplace relationship the key to finding meaning on the job the ethical life podcast the next x crypto to invest in a cardano ada and ripple xrp holder seek stronger bull run play are workplace relationship the key to finding meaning on the job the ethical life podcast xrp news today why investor are choosing this defi utility token over ripple clear creek isd trustee approve over k in capital project are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast america bankruptcy wave ha surpassed the pandemicand it getting worse josh kosnicks five bridge answer whats next when the hustle fails highflying stock set for a pullback sp hit record high a investor await nvidia result reuters these analyst increase their forecast on ncino following betterthanexpected q earnings xrp bitcoin or eth here which coin user predict to perform best until trump critic inside fema put on indefinite leave after blasting cut in dissent letter up fintech share drop after strong q result what you need to know subsea awarded contract offshore turkiye rfk jr make good on promise to end covid vaccine mandate biontech tumble this economic sugar high wont last crfb warns touting analysis predicting longterm stagnation and billion of annual borrowing through the latest trump effort to control u capital expands to union station bytedance target billion valuation a revenue exceed meta sharp technology soar after insider buy and m solana treasury plan water wellness summit offer expert analysis recommendation for waterborne disease prevention the death of reaganomics trump break with longtime gop economic doctrine first commerce credit union donates for student scholarship buffalo diocese abuse settlement increase to million downtown san jose apartment complex land construction loan downtown san jose apartment complex land construction loan bank of montreal analyst boost their forecast after q result fargo agrees to jail rate increase after exhausting discussion building your organization next generation of leader no college degree here are job where can still earn figure no college degree here are job where can still earn figure mdot suspending construction lifting traffic restriction for labor day weekend how coolvu is empowering entrepreneur and protecting small business powell see the light in his final jackson hole talk my husband sold our house behind my back and kept every dime well now it my turn to cut him off uvalde cisd considers new law firm a trust in current agency falter following document issue johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder these analyst boost their forecast on echostar delta to pay million to resolve fuel dump lawsuit investigation alert elanco animal health incorporated driven brand holding hasbro and transmedics johnson fistel pllp investigates claim on behalf of investor kelowna councillor wonder if the city should stop density bonusing program kelowna arctic pablo coin raise m in presale one of the top meme coin to invest a dogecoin and shiba inu rally make cracker barrel a winner again trump celebrates logo reversal nprs all thing considered name scott detrow a new fulltime host johnson fistel pllp investigates constellation brand atkore domino pizza and fmc corporation on behalf of longterm shareholder innout primanti bros gone after one year on high street these analyst revise their forecast on okta after upbeat q earnings rbc city national bank is back on front foot ceo say nvidias upstart chinese rival cambricon just showed growth but dont get too excited trump is forcing the economy to bend to his will only one person can stop him the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station another power company eyeing northwestern ontario city for solar farm guess investor alert by the former attorney general of louisiana kahn swick foti llc investigates adequacy of price and process in proposed sale of guess inc ge executive order open door to alternative asset in k key consideration for plan fiduciary im rooting for female founder comeback and for the end of branding woman from girlboss to tradwife and all the way down the best walmart labor day deal on kitchen bestseller university of phoenix leadership present at greater phoenix chamber foundation workforce summit university of phoenix leadership present at greater phoenix chamber foundation workforce summit the latest trump effort to control u capital expands to union station mongodb to rally around here are top analyst forecast for wednesday will credit card interest rate finally drop this september cross river and sightline team on gamingfocused debit card tom cotton target tax status of terroristsupporting youth movement vertical aerospace shortinterest collapse signal shifting market sentiment food and chemical unpacked epr you keeping up podcast unpacking the latest option trading trend in carvana decoding bank of america option activity whats the big picture oktas option a look at what the big money is thinking attention cio it is just one week away register now florida csuite executive invited to forecasting the future analyst projection for synopsys crowdstrike likely to report lower q earnings these most accurate analyst revise forecast ahead of earnings call analyst assess lineage cell therapeutic what you need to know analyst expectation for omega healthcare invtss future larkins investigation expands to indianapolis in now offering comprehensive investigative and tscm service what analyst rating have to say about compass let talk indianola mayor steve richardson analyst expectation for eli lillys future texas new proxy advisor disclosure law key detail for shareholder and company ahead of september pe ratio insight for bread finl hldgs analyst expectation for essex property trust future coach tory burch and more designer bag are up to off on amazon save up to on dyson dewalt anker adidas and more during ebays th anniversary sale maga loses it after minneapolis mayor emotional speech on shooting voter lose in redistricting game texas republican are wrong to start this tit for tat fight voter lose in redistricting game texas republican are wrong to start this tit for tat fight trump tell supreme court he shouldnt have to spend foreign aid approved by congress fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr federal prosecutor fail to indict sandwich slinger exdoj employee on assault charge report gerrymandering is controversial but the alternative is worse fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr attorney for jack smith respond to federal watchdog probe fulton county commissioner risk jail time for not appointing republican to election board dc mayor masked ice agent and outoftown national guard are ineffective axios lehigh valley police department shared driver comical excuse during speed enforcement detail ukraine will allow men to leave country exploring trend how immigration shape our region from cracker barrel to bud light trump weighs in on another corporate controversy un warns gaza famine expanding a aid group decry israeli siege riley push bill for rural hospital funding gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule trouble finding tea global matcha shortage take toll on bay area business white nationalist agenda minority in front line of trump policy target minneapolis mayor jacob frey slammed for mocking prayer after the catholic school shooting gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder mixed report of russian force holding ground in dnipropetrovsk ice is suddenly showing up in california hospital worker want more guidance on what to do ice is suddenly showing up in california hospital worker want more guidance on what to do the not so dormant commerce clause watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue congressional candidate in arizona debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue protester to assemble on labor day magic johnson turned down a deal of a lifetime in boy did i make a mistake im still kicking myself offset vow to never get married again warns men against it too mary spencer youre not too young to make an estate plan commentary why is trump going after the smithsonian museum gov tony evers renews appeal for fema help following milwaukeearea flooding a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know executive order open door to alternative asset in k key consideration for plan fiduciary abrego garcia cannot be deported before october hearing judge say council in burnaby bc call for israel arm embargo metro vancouver south african politician criticized by trump is found guilty of hate speech u envoy cut lebanon trip short amid protest outrage over press comment trump say liberal donor george soros and son should be criminally charged bolivian court order the release of a prominent rightwing opposition leader fema worker put on leave after signing letter warning of trump overhaul of the agency how wes moore can stand up for the national guard guest commentary bengalmc air cushion catamaran aim to be the navy future ultraadaptable combat ship newton is removing italian flag color from street again russian force break into another region of ukraine with peace effort stuck green destry covington table drinking area vote again native american housing advocate urge congress to renew affordable housing law nyc mayor race eric adam label democratic socialist mamdani a communist echoing a frequent trump attack trump military invasion is cleaning up dcliterally denmark summons u envoy over suspected influence campaign in greenland debate over book page pit cultural concern against free access asking eric im a loyal person but my husband emotional affair ha me unable to trust him republican nominated to replace sen darin smith joseph kibler running for wyoming governor credit union deliver big return for community through cdfis new parkingmeter hour added for el cajon boulevard surrounding area top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show majority of voter oppose deploying national guard to dc quinnipiac university national poll find support drop for u military aid to israel a think israel is committing genocide in gaza quinnipiac university poll u federal judge rule wisconsin judge cannot claim immunity in immigration obstruction case jared kushner participates in gaza meeting at the white house source say watch labor leader give trump the business for hurting worker top florida official say alligator alcatraz will likely be empty within day email show morris a a wave of shooting roils minneapolis leave the national guard at home a deadly florida truck crash ha fueled an immigration fight here what to know a deadly florida truck crash ha fueled an immigration fight here what to know</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>silver stabilizes above a mean reversion structure hold ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard fashion model reckon with ai model and digital clone after controversial ad appears in vogue ai profit window is wide open here how to time it from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast safer foundation to host open house at new employment service location in rock island are workplace relationship the key to finding meaning on the job the ethical life podcast the next x crypto to invest in a cardano ada and ripple xrp holder seek stronger bull run play are workplace relationship the key to finding meaning on the job the ethical life podcast xrp news today why investor are choosing this defi utility token over ripple clear creek isd trustee approve over k in capital project are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast america bankruptcy wave ha surpassed the pandemicand it getting worse josh kosnicks five bridge answer whats next when the hustle fails highflying stock set for a pullback sp hit record high a investor await nvidia result reuters these analyst increase their forecast on ncino following betterthanexpected q earnings xrp bitcoin or eth here which coin user predict to perform best until trump critic inside fema put on indefinite leave after blasting cut in dissent letter up fintech share drop after strong q result what you need to know subsea awarded contract offshore turkiye rfk jr make good on promise to end covid vaccine mandate biontech tumble this economic sugar high wont last crfb warns touting analysis predicting longterm stagnation and billion of annual borrowing through the latest trump effort to control u capital expands to union station bytedance target billion valuation a revenue exceed meta sharp technology soar after insider buy and m solana treasury plan water wellness summit offer expert analysis recommendation for waterborne disease prevention the death of reaganomics trump break with longtime gop economic doctrine first commerce credit union donates for student scholarship buffalo diocese abuse settlement increase to million downtown san jose apartment complex land construction loan downtown san jose apartment complex land construction loan bank of montreal analyst boost their forecast after q result fargo agrees to jail rate increase after exhausting discussion building your organization next generation of leader no college degree here are job where can still earn figure no college degree here are job where can still earn figure mdot suspending construction lifting traffic restriction for labor day weekend how coolvu is empowering entrepreneur and protecting small business powell see the light in his final jackson hole talk my husband sold our house behind my back and kept every dime well now it my turn to cut him off uvalde cisd considers new law firm a trust in current agency falter following document issue johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder these analyst boost their forecast on echostar delta to pay million to resolve fuel dump lawsuit investigation alert elanco animal health incorporated driven brand holding hasbro and transmedics johnson fistel pllp investigates claim on behalf of investor kelowna councillor wonder if the city should stop density bonusing program kelowna arctic pablo coin raise m in presale one of the top meme coin to invest a dogecoin and shiba inu rally make cracker barrel a winner again trump celebrates logo reversal nprs all thing considered name scott detrow a new fulltime host johnson fistel pllp investigates constellation brand atkore domino pizza and fmc corporation on behalf of longterm shareholder innout primanti bros gone after one year on high street these analyst revise their forecast on okta after upbeat q earnings rbc city national bank is back on front foot ceo say nvidias upstart chinese rival cambricon just showed growth but dont get too excited trump is forcing the economy to bend to his will only one person can stop him the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station another power company eyeing northwestern ontario city for solar farm guess investor alert by the former attorney general of louisiana kahn swick foti llc investigates adequacy of price and process in proposed sale of guess inc ge executive order open door to alternative asset in k key consideration for plan fiduciary im rooting for female founder comeback and for the end of branding woman from girlboss to tradwife and all the way down the best walmart labor day deal on kitchen bestseller university of phoenix leadership present at greater phoenix chamber foundation workforce summit university of phoenix leadership present at greater phoenix chamber foundation workforce summit the latest trump effort to control u capital expands to union station mongodb to rally around here are top analyst forecast for wednesday will credit card interest rate finally drop this september cross river and sightline team on gamingfocused debit card tom cotton target tax status of terroristsupporting youth movement vertical aerospace shortinterest collapse signal shifting market sentiment food and chemical unpacked epr you keeping up podcast unpacking the latest option trading trend in carvana decoding bank of america option activity whats the big picture oktas option a look at what the big money is thinking attention cio it is just one week away register now florida csuite executive invited to forecasting the future analyst projection for synopsys crowdstrike likely to report lower q earnings these most accurate analyst revise forecast ahead of earnings call analyst assess lineage cell therapeutic what you need to know analyst expectation for omega healthcare invtss future larkins investigation expands to indianapolis in now offering comprehensive investigative and tscm service what analyst rating have to say about compass let talk indianola mayor steve richardson analyst expectation for eli lillys future texas new proxy advisor disclosure law key detail for shareholder and company ahead of september pe ratio insight for bread finl hldgs analyst expectation for essex property trust future coach tory burch and more designer bag are up to off on amazon save up to on dyson dewalt anker adidas and more during ebays th anniversary sale maga loses it after minneapolis mayor emotional speech on shooting voter lose in redistricting game texas republican are wrong to start this tit for tat fight voter lose in redistricting game texas republican are wrong to start this tit for tat fight trump tell supreme court he shouldnt have to spend foreign aid approved by congress fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr federal prosecutor fail to indict sandwich slinger exdoj employee on assault charge report gerrymandering is controversial but the alternative is worse fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr attorney for jack smith respond to federal watchdog probe fulton county commissioner risk jail time for not appointing republican to election board dc mayor masked ice agent and outoftown national guard are ineffective axios lehigh valley police department shared driver comical excuse during speed enforcement detail ukraine will allow men to leave country exploring trend how immigration shape our region from cracker barrel to bud light trump weighs in on another corporate controversy un warns gaza famine expanding a aid group decry israeli siege riley push bill for rural hospital funding gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule trouble finding tea global matcha shortage take toll on bay area business white nationalist agenda minority in front line of trump policy target minneapolis mayor jacob frey slammed for mocking prayer after the catholic school shooting gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder mixed report of russian force holding ground in dnipropetrovsk ice is suddenly showing up in california hospital worker want more guidance on what to do ice is suddenly showing up in california hospital worker want more guidance on what to do the not so dormant commerce clause watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue congressional candidate in arizona debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue protester to assemble on labor day magic johnson turned down a deal of a lifetime in boy did i make a mistake im still kicking myself offset vow to never get married again warns men against it too mary spencer youre not too young to make an estate plan commentary why is trump going after the smithsonian museum gov tony evers renews appeal for fema help following milwaukeearea flooding a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know executive order open door to alternative asset in k key consideration for plan fiduciary abrego garcia cannot be deported before october hearing judge say council in burnaby bc call for israel arm embargo metro vancouver south african politician criticized by trump is found guilty of hate speech u envoy cut lebanon trip short amid protest outrage over press comment trump say liberal donor george soros and son should be criminally charged bolivian court order the release of a prominent rightwing opposition leader fema worker put on leave after signing letter warning of trump overhaul of the agency how wes moore can stand up for the national guard guest commentary bengalmc air cushion catamaran aim to be the navy future ultraadaptable combat ship newton is removing italian flag color from street again russian force break into another region of ukraine with peace effort stuck green destry covington table drinking area vote again native american housing advocate urge congress to renew affordable housing law nyc mayor race eric adam label democratic socialist mamdani a communist echoing a frequent trump attack trump military invasion is cleaning up dcliterally denmark summons u envoy over suspected influence campaign in greenland debate over book page pit cultural concern against free access asking eric im a loyal person but my husband emotional affair ha me unable to trust him republican nominated to replace sen darin smith joseph kibler running for wyoming governor credit union deliver big return for community through cdfis new parkingmeter hour added for el cajon boulevard surrounding area top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show majority of voter oppose deploying national guard to dc quinnipiac university national poll find support drop for u military aid to israel a think israel is committing genocide in gaza quinnipiac university poll u federal judge rule wisconsin judge cannot claim immunity in immigration obstruction case jared kushner participates in gaza meeting at the white house source say watch labor leader give trump the business for hurting worker top florida official say alligator alcatraz will likely be empty within day email show morris a a wave of shooting roils minneapolis leave the national guard at home a deadly florida truck crash ha fueled an immigration fight here what to know a deadly florida truck crash ha fueled an immigration fight here what to know</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-0.9949</v>
+      </c>
+      <c r="O47" t="n">
+        <v>121</v>
+      </c>
+      <c r="P47" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>181</v>
+      </c>
+      <c r="S47" t="n">
+        <v>72</v>
+      </c>
+      <c r="T47" t="n">
+        <v>210</v>
+      </c>
+      <c r="U47" t="n">
+        <v>135</v>
+      </c>
+      <c r="V47" t="n">
+        <v>70</v>
+      </c>
+      <c r="W47" t="n">
+        <v>34</v>
+      </c>
+      <c r="X47" t="n">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,6 +4128,84 @@
         <v>38</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6460.259765625</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6491.759765625</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6444.56982421875</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6489.27978515625</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4234840000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.0063981842935716</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>judge block kari lake tasked to dismantle voa from firing it director annunciation mass shooting what we know about the shooter motive stock add a bit to their record on wall street flyw class action reminder flyw investor with large loss should contact robbins llp for information about the lead plaintiff deadline in the flywire corporation class action lawsuit atlas energy report second quarter financial result shareholder notice faruqi faruqi llp investigates claim on behalf of investor of altimmune ehc investor news if you have suffered loss in encompass health corporation nyse ehc you are encouraged to contact the rosen law firm about your right coinbase to monetize bitcointoethereum rotation through trading volume cfo say intel took trump deal to remove uncertainty around chip act billion los gatos property sale twobedroom home sell for million los gatos property sale twobedroom home sell for million raising cane to open more restaurant in september how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained fort smith weighs m in water upgrade a demand grows market expert say ozak ai might outperform ethereum in next bull run food hub planned across treaty territory to combat food insecurity xrp news today analyst warns dont sell xrp yet lawsuit win etf catalyst may lift price california face high pump price a phillips shuts la refinery the federal government is taking over dc union station what doe that mean the federal government is taking over dc union station what doe that mean u put official gdp data on nine blockchains in historic trumpera crypto push is ada price mirroring the breakout pattern a holder look for the next x bet big on remittix missing yearold boy with autism killed by alligator in new orleans police finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service hormel share face worst day on record a pork and other cost surge gbank financial holding inc is pleased to share the press release of boltbetz nike put finishing touch on a corporate overhaul more layoff ahead taco bell reconsiders voice ai after seeing mixed result tesla sale plunge again in europe a anger at musk keep buyer away for th month in a row yahoo finance northwood plaza owner defends work at former great eastern council want action gbank financial holding inc is pleased to share the press release of boltbetz will a reverse mortgage impact your social security or medicare benefit taiwan prosecutor charge people for allegedly stealing tsmc trade secret consumer watchdog public interest group to legislator dont let newsom sell out real utility rate reform in eleventh hour deal for utilitybacked western grid proposal and wildfire fund retail roundup key winner and loser after q earnings gbank financial holding inc is pleased to share the press release of boltbetz guardian officially release million veteran after disappointing season small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption beef and nut price have surged and thats driving hormels stock to it biggest drop ever fresno council to vote on m plan for west fresno affordable housing jcpenneys closing down sale spread to two more location after shutdown continue major airline add route with low flight cost challenging a top rival meta is racing the clock to launch it newest llama ai model this year business insider reykjavik energy green bond auction result fed cook an unintentional clerical error may have been behind the mortgage dispute ap sport summarybrief at pm edt earthwise advertising investor awareness campaign bluerock total income real estate fund shareholder receive iss and glass lewis recommendation to support key proposal in connection with listing of the fund on the nyse a sea war brew off gambia a desperate local fisherman attack foreign vessel and each other labor day deal alert heydude is offering an extra off top style city pivot after apex rescinds rosecrans airport lease agreement best ai chatbots and key statistic of stockton mark oneyear anniversary of staart app with conference powerball player win in texas where wa the lucky ticket sold florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown the probability machine trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post politico who are the most valuable nfl team cowboy b top forbes list for instacart offer indie grocer ecommerce tool with mdi partnership naples set tax rate at postal service across the world to suspend u delivery after trump end tariff exemption casco set tax rate at credo stock notch record high ahead of earnings report grocery chain to close maryland location campaign finance board again denies matching fund to mayor adam seager marine acquires rk marina on rushford lake u economy grew percent in q beating prior estimate denim trend boost abercrombie a outlook stock climb treasury secretary bessent capital market are roaring back powerball jackpot nears billion ahead of saturday drawing trump pick for un aviation office ha long history donating to dems nikki haley nyseg rge to upgrade high voltage line substation across ny state how michael polk growth culture drove performance at newell brand and beyond trump look to fire transportation regulator ahead of rail merger a closer look at enphase energy option market dynamic stonepeak buy fort worth logistics property freeland to host history walk and cemetery tour for th anniversary rwanda say deportee arrived from the u in august under agreement with washington ap business summarybrief at pm edt cdc crisis triggered by upcoming vaccine meeting leading to director firing former yankee mark teixeira running for congress a republican apparently anyone can be an immigration judge in trump america white house confirms trump fired cdc director after she refused to resign woman at center of viral rochester video say she moved intends to fight charge sunday voting choice given to county by state board trump renews citizenship requirement waived since noem hit back at fema critic reveals vision for disaster relief agency the federal government is taking over dc union station what doe that mean npr former golden triangle development leader conduct would harm every member of this community xi put axis of u enemy on parade with putin kim in beijing former mlb star mark teixeira announces run for texas congressional seat trump administration asks military base near chicago for support on immigration operation whatever happened to the woman in the no sex for fish group whatever happened to the woman in the no sex for fish group minneapolis mayor we need a statewide and a federal ban on assault weapon cdc director arrives at office to find dead deer with fired carved into it what to know after the u deports more migrant to africa the latest trump administration asks military base near chicago for support on immigration gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap at least migrant detained by ice in san francisco a arrest soar iran is facing a return of un sanction what happens now immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started exclusive gop smell blood in water over defeated dem exsens vulnerability karoline leavitt take jen psaki to task over her attack on prayer following tragic catholic school shooting fresno council to vote on m plan for west fresno affordable housing governor pay tribute to buttearea veteran still serving veteran closure of florida alligator alcatraz immigration detention center can proceed judge say mass sen warren launch probe over shuttering of public corruption unit at justice dept fbi leavitt slam insensitive psaki on prayer comment after minnesota shooting montgomery county ready to combat mosquito with targeted spraying in windlestrae park amid west nile concern opinion gov newsom playing for a tie in national redistricting battle leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting congress probe wikipedia over antiisrael prokremlin content manipulation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation leavitt slam insensitive psaki on prayer comment after minnesota shooting fed lisa cook sue trump over move to fire her is it ever legal to pas a school bus in new jersey u to sell ukraine extendedrange missile resident have a chance to weigh in on city chicken sept texas governor greg abbott revise special legislative session agenda to enhance law enforcement privacy election integrity election commission panel call for a shakeup in how hawaii vote ecuadorian man arrested in maine sue immigration official alleging unlawful detention deadeyed travis kelce nod at bow tie option for cat ring bearer trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post trump federal takeover of dc could do irreparable damage to policecommunity relation rfk jr say cdc must deliver on trump agenda after white house fire director flagging flag burner again wife of greencard holder detained by ice speaks outlots of tear shenandoah to rework park master plan following resident pushback watchdog group sue for record on spying targeting trump associate michael caputo tong warns of recruitment scam targeting ct job seeker white house is not happy with view cohost for her comment on latino trumpers campaign finance board again denies matching fund to mayor adam ap business summarybrief at pm edt hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness schumer jeffries call on gop leader to meet to avoid government shutdown bondi patel to testify before congress amid epstein fallout bondi patel to testify before congress amid epstein fallout european power hit iran with pre sanction a pressure for nuclear negotiation hoosier gop legislative leader break redistricting silence no business a usual public rally monday at shorey park judge frank caprios death leaf mourner remembering his compassion that drew many online fan montgomery county executive celebrates new affordable housing milestone in montgomery village uno study offer firstever look into labor trafficking in nebraska lt governor david wasinger launch missouri state employee charitable campaign in jefferson city trump unprecedented firing of fed governor lisa cook raise untested question</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>judge block kari lake tasked to dismantle voa from firing it director annunciation mass shooting what we know about the shooter motive stock add a bit to their record on wall street flyw class action reminder flyw investor with large loss should contact robbins llp for information about the lead plaintiff deadline in the flywire corporation class action lawsuit atlas energy report second quarter financial result shareholder notice faruqi faruqi llp investigates claim on behalf of investor of altimmune ehc investor news if you have suffered loss in encompass health corporation nyse ehc you are encouraged to contact the rosen law firm about your right coinbase to monetize bitcointoethereum rotation through trading volume cfo say intel took trump deal to remove uncertainty around chip act billion los gatos property sale twobedroom home sell for million los gatos property sale twobedroom home sell for million raising cane to open more restaurant in september how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained fort smith weighs m in water upgrade a demand grows market expert say ozak ai might outperform ethereum in next bull run food hub planned across treaty territory to combat food insecurity xrp news today analyst warns dont sell xrp yet lawsuit win etf catalyst may lift price california face high pump price a phillips shuts la refinery the federal government is taking over dc union station what doe that mean the federal government is taking over dc union station what doe that mean u put official gdp data on nine blockchains in historic trumpera crypto push is ada price mirroring the breakout pattern a holder look for the next x bet big on remittix missing yearold boy with autism killed by alligator in new orleans police finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service hormel share face worst day on record a pork and other cost surge gbank financial holding inc is pleased to share the press release of boltbetz nike put finishing touch on a corporate overhaul more layoff ahead taco bell reconsiders voice ai after seeing mixed result tesla sale plunge again in europe a anger at musk keep buyer away for th month in a row yahoo finance northwood plaza owner defends work at former great eastern council want action gbank financial holding inc is pleased to share the press release of boltbetz will a reverse mortgage impact your social security or medicare benefit taiwan prosecutor charge people for allegedly stealing tsmc trade secret consumer watchdog public interest group to legislator dont let newsom sell out real utility rate reform in eleventh hour deal for utilitybacked western grid proposal and wildfire fund retail roundup key winner and loser after q earnings gbank financial holding inc is pleased to share the press release of boltbetz guardian officially release million veteran after disappointing season small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption beef and nut price have surged and thats driving hormels stock to it biggest drop ever fresno council to vote on m plan for west fresno affordable housing jcpenneys closing down sale spread to two more location after shutdown continue major airline add route with low flight cost challenging a top rival meta is racing the clock to launch it newest llama ai model this year business insider reykjavik energy green bond auction result fed cook an unintentional clerical error may have been behind the mortgage dispute ap sport summarybrief at pm edt earthwise advertising investor awareness campaign bluerock total income real estate fund shareholder receive iss and glass lewis recommendation to support key proposal in connection with listing of the fund on the nyse a sea war brew off gambia a desperate local fisherman attack foreign vessel and each other labor day deal alert heydude is offering an extra off top style city pivot after apex rescinds rosecrans airport lease agreement best ai chatbots and key statistic of stockton mark oneyear anniversary of staart app with conference powerball player win in texas where wa the lucky ticket sold florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown the probability machine trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post politico who are the most valuable nfl team cowboy b top forbes list for instacart offer indie grocer ecommerce tool with mdi partnership naples set tax rate at postal service across the world to suspend u delivery after trump end tariff exemption casco set tax rate at credo stock notch record high ahead of earnings report grocery chain to close maryland location campaign finance board again denies matching fund to mayor adam seager marine acquires rk marina on rushford lake u economy grew percent in q beating prior estimate denim trend boost abercrombie a outlook stock climb treasury secretary bessent capital market are roaring back powerball jackpot nears billion ahead of saturday drawing trump pick for un aviation office ha long history donating to dems nikki haley nyseg rge to upgrade high voltage line substation across ny state how michael polk growth culture drove performance at newell brand and beyond trump look to fire transportation regulator ahead of rail merger a closer look at enphase energy option market dynamic stonepeak buy fort worth logistics property freeland to host history walk and cemetery tour for th anniversary rwanda say deportee arrived from the u in august under agreement with washington ap business summarybrief at pm edt cdc crisis triggered by upcoming vaccine meeting leading to director firing former yankee mark teixeira running for congress a republican apparently anyone can be an immigration judge in trump america white house confirms trump fired cdc director after she refused to resign woman at center of viral rochester video say she moved intends to fight charge sunday voting choice given to county by state board trump renews citizenship requirement waived since noem hit back at fema critic reveals vision for disaster relief agency the federal government is taking over dc union station what doe that mean npr former golden triangle development leader conduct would harm every member of this community xi put axis of u enemy on parade with putin kim in beijing former mlb star mark teixeira announces run for texas congressional seat trump administration asks military base near chicago for support on immigration operation whatever happened to the woman in the no sex for fish group whatever happened to the woman in the no sex for fish group minneapolis mayor we need a statewide and a federal ban on assault weapon cdc director arrives at office to find dead deer with fired carved into it what to know after the u deports more migrant to africa the latest trump administration asks military base near chicago for support on immigration gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap at least migrant detained by ice in san francisco a arrest soar iran is facing a return of un sanction what happens now immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started exclusive gop smell blood in water over defeated dem exsens vulnerability karoline leavitt take jen psaki to task over her attack on prayer following tragic catholic school shooting fresno council to vote on m plan for west fresno affordable housing governor pay tribute to buttearea veteran still serving veteran closure of florida alligator alcatraz immigration detention center can proceed judge say mass sen warren launch probe over shuttering of public corruption unit at justice dept fbi leavitt slam insensitive psaki on prayer comment after minnesota shooting montgomery county ready to combat mosquito with targeted spraying in windlestrae park amid west nile concern opinion gov newsom playing for a tie in national redistricting battle leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting congress probe wikipedia over antiisrael prokremlin content manipulation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation leavitt slam insensitive psaki on prayer comment after minnesota shooting fed lisa cook sue trump over move to fire her is it ever legal to pas a school bus in new jersey u to sell ukraine extendedrange missile resident have a chance to weigh in on city chicken sept texas governor greg abbott revise special legislative session agenda to enhance law enforcement privacy election integrity election commission panel call for a shakeup in how hawaii vote ecuadorian man arrested in maine sue immigration official alleging unlawful detention deadeyed travis kelce nod at bow tie option for cat ring bearer trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post trump federal takeover of dc could do irreparable damage to policecommunity relation rfk jr say cdc must deliver on trump agenda after white house fire director flagging flag burner again wife of greencard holder detained by ice speaks outlots of tear shenandoah to rework park master plan following resident pushback watchdog group sue for record on spying targeting trump associate michael caputo tong warns of recruitment scam targeting ct job seeker white house is not happy with view cohost for her comment on latino trumpers campaign finance board again denies matching fund to mayor adam ap business summarybrief at pm edt hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness schumer jeffries call on gop leader to meet to avoid government shutdown bondi patel to testify before congress amid epstein fallout bondi patel to testify before congress amid epstein fallout european power hit iran with pre sanction a pressure for nuclear negotiation hoosier gop legislative leader break redistricting silence no business a usual public rally monday at shorey park judge frank caprios death leaf mourner remembering his compassion that drew many online fan montgomery county executive celebrates new affordable housing milestone in montgomery village uno study offer firstever look into labor trafficking in nebraska lt governor david wasinger launch missouri state employee charitable campaign in jefferson city trump unprecedented firing of fed governor lisa cook raise untested question</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.9982</v>
+      </c>
+      <c r="O48" t="n">
+        <v>77</v>
+      </c>
+      <c r="P48" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>127</v>
+      </c>
+      <c r="S48" t="n">
+        <v>59</v>
+      </c>
+      <c r="T48" t="n">
+        <v>179</v>
+      </c>
+      <c r="U48" t="n">
+        <v>133</v>
+      </c>
+      <c r="V48" t="n">
+        <v>37</v>
+      </c>
+      <c r="W48" t="n">
+        <v>37</v>
+      </c>
+      <c r="X48" t="n">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X48"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4206,6 +4206,84 @@
         <v>41</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6415.5400390625</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6416.5400390625</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6360.580078125</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6401.509765625</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4784000000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0069222799368615</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>hows the market doe ownership go past the topsoil fresh stock on jim cramers radar juneteenth organizer get funding to repair modernize building panda express owns other restaurant chain do you know which one fed rate cut still on track no firework after nvidia earnings federal government post billion deficit from april to june canada whats going on with broadcom stock friday oakland unified school district looking to shed nearly million from budget is it a bot or not ticketings next big legal fight could reshape the resale industry a model for understanding with edward kaplan smlr investor have opportunity to lead semler scientific inc security fraud lawsuit first filed by the rosen law firm rock tech lithium announces offering of up to million the persistent pitfall of taxpayer funded campaign berkshire hillsbrookline merger nears completion retailer warn trump tariff will trigger consumer price explosion who will he blame boing boing nvidia ceo say ai will actually make u busier in the future gizmodo is amazon falling behind in the cloud computing battle brutally honest way to finance your startup dmv may owe you s and have no obligation to let you know wa being held in just a single case qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada should the federal reserve cut rate next month should the federal reserve cut rate next month hope gas responds to criticism in it pipeline program ratehike case raising cane to open ann arbor location september th the company second in metro detroit trump administration kill wasteful funding for humboldt bay offshore wind project sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion ardot seeking public comment on proposed disadvantaged business enterprise goal for why you should think twice before buying private equity in your k nasb financial inc declares cash dividend on common stock sunblock charcoal and powerball holiday weekend lottery drawing worth billion ap news ulta beauty delivers strong quarter investor brush off the glow thought i wa going to die tunisian singer detained for week fight deportation while trying to finish music small business joint venture win coast guard cyber contract dupont to sell kevlar business for billion the manufacturer life insurance company grows position in tesla inc tsla stock market news today market slide a chip stock weigh spsp complete index seeking alpha layoff hit international paper jb hunt hormel and more the orange peel first year put asheville on the map now staffer hope to buy it cv walgreens now require prescription for covid vaccine in colorado the denver post in hong kong eric trump lauds growing influence of crypto the new york time forecasting the future analyst projection for oneok what the option market tell u about mastercard lazr investor have opportunity to lead luminar technology inc security fraud lawsuit sword group availability of the h financial report sword group h report of the liquidity agreement contracted with oddo bhf procter gamble unusual option activity forecasting the future analyst projection for dt midstream dows option frenzy what you need to know pce inflation flat but core sticky implication for fed september meeting analyst expectation for targa resourcess future breaking down karooooo analyst share their view segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase a glimpse into the expert outlook on cheniere energy through analyst is rivian automotive gaining or losing market support peering into extreme networkss recent short interest let talk indianola kwik star ribbon cutting expert outlook snapon through the eye of analyst is flex gaining or losing market support pe ratio insight for bank of nova scotia let talk knoxville planning and zoning administrator nathan parch part two segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase u government publishes gdp data on bitcoin ethereum blockchains home price in okanagan and kamloops area may be levelling housewise chainlink link price movement face hurdle litecoin target rally while cold wallet hold roi edge major discount on outdoor furniture costway dining set off at target bytedance hit b valuation a q revenue surge to b energy exchange electronx earns cftc designated market and clearing approval how senior can borrow home equity without refinancing now crypto news today coinshares profit jump avalanche transaction rise gumi add xrp here why serve robotics surged this week savvy shopper save over k in year by extreme couponing she scored k of jcpenney cookware for just backtoschool sale tax holiday the edmund fitzgerald and a state microbe theyre among state bill in august should you buy lucid stock ahead of it for reverse stock split bitcoin drop below a xrp slide below and eth dogecoin wobble shopping labor day furniture sale tip to bargain for the best price ollies bargain earnings suggest analyst underestimate longterm potential no ruling friday on trump attempt to fire fed official the credit race closing the perception gap to win welcome to the new made in china era and it look a lot different dell struggle to protect margin a supply chain cost mount cracker barrel ditched it new logo but it also got rid of something else labubu doll and affordable latte why chinese brand are betting big on the u business insider mycarrier portal and carrier assure integrate to make carrier vetting easier cracker barrel is still deep in dei despite the return of uncle herschel former trans mountain ceo to head major project office canada cracker barrel did more than just ditch it logo after maga meltdown the daily beast cracker barrel new logo wa pitiful one of chain original executive say anthony brown maryland legal victory show prudent use of resource reader commentary atlanta becomes largest u metro without a printed daily newspaper a journalconstitution go digital techstock skid sends nasdaq sharply lower live stockmarket update understanding the benefit and risk of ai agent university of northern iowa to open finance and real estate analytics lab for business eli lilly is proof that wall street star dont have to be tech titan trump fire democratic member from transportation board just before it considers the largest railroad merger in history marvell sink a weak data center outlook stokes custom ai chip worry reuters mount logan capital inc shareholder approve previously announced business combination with degree capital corp court block trump effort to end protected status for venezuelan mamdani team with sharpton to threaten wall street upcoming upgrade to holocaust museum exhibit spark some staff concern source trump planning immigration crackdown in chicago next week dhs source say gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber migrant defer their american dream to seek asylum in mexico bonus editorial cartoon for aug alabama town first black mayor reelected after being locked out of office lawyer who led karen read defense one step closer to joining team for civil suit trump move to cut bn in foreign aid already approved by congress rubio revoke visa for palestinian official denying address at un meeting alabama town first black mayor reelected year after he say white resident locked him out of office cbs news can tv help prepare for invasion jd vance say there thing dems should learn from trump and critic cant believe he serious jd vance say there thing dems should learn from trump and critic cant believe he serious abrego garcia asks for gag order on bondi noem meet bill pulte the trump housing official at the center of the latest fed controversy abrego garcia asks for gag order on bondi noem judge weighs request to block trump firing of fed governor lisa cook abrego garcia asks for gag order on bondi noem contract talk fail between alberta government and teacher possible strike loom alberta republican joni ernst will not seek reelection source say abrego garcia asks for gag order on bondi noem trump yank kamala harris bidenextended taxpayerfunded secret service protection before book tour susan estrich the epitome of dumbness judge hears argument on lisa cook attempted firing by trump administration psc answer preston county commission objection to marl project corruption allegation impact argentina president mileis popularity trump block b in foreign aid congress okd using maneuver last seen nearly year ago trump block b in foreign aid congress okd using maneuver last seen nearly year ago mackinac island police chief to resign citing ongoing friction with city council a lament for the shrinking middle class reader commentary dear annie unfaithful fiancee tell me to stop living in the past appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan a trumpbrokered peace deal in the south caucasus is hopeful but incomplete many state employeefriendly labor law take effect a nlrb remains quorumless benton county to display in god we trust in all public building by oct everyone on x point and laugh at dingus gungrabber who share pic of bullet scattered on his street democrat some republican cry outrage over trump use of rare tactic to withhold approved foreign aid funding lori falce year of thought and prayer appeal court say uk asylumseekers can stay at hotel dc federal judge to weigh order blocking fed gov lisa cook firing ahead of interest rate meeting let talk knoxville planning and zoning administrator nathan parch part two donald trump war on culture is not a sideshow japan india to deepen security economic tie amid u tariff ai is ummasking ice officer can washington do anything about it politico public trust in election increase with clear fact sen ernst of iowa is expected to announce next month that she wont run for reelection in u revoke visa of palestinian official ahead of un general assembly fox news star call out trump ally over apparent hypocrisy this is the same thing sen ernst of iowa is expected to announce next month that she wont run for reelection in ap news fox news star call out trump ally over apparent hypocrisy this is the same thing free speech unmuted president trump executive order on flag desecration it a joke san jose mayor slam california legislature over lack of prop funding ransomware attack targeting pa attorney general lead to case delay susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider chicago is in the trump administration sight for it next immigration crackdown chicago is in the trump administration sight for it next immigration crackdown trump admin plan immigration enforcement surge in boston politico a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows kilmar abrego garcia asks for gag order against pam bondi kristi noem kilmar abrego garcia asks for gag order against pam bondi kristi noem texas gov greg abbott sign new congressional redistricting map president trump requested kimball shinkoskey explain the law talk for trump riviera in gaza persist a israel push deeper into gaza city france germany vow to up pressure on ogre putin bankruptcy for north dakota and western minnesota published aug trump administration to cut plus job at voice of america best business line of credit in flexible small business funding option for growth and emergency adhesive dowel veneer the industrial choice shaping mass timber verizon down how to fix so modeonly issue in phone amid outage hindustan time hindustan time what would the fed do in a tie vote it not clear and the bank of england had to break a deadlock this month can you use milwaukee battery on harbor freight tool ulster county rail trail study to be contracted to new paltzbased consulting firm tim walz admits vp bid might have hurt him with voter in home state judge delay septum rate increase additional service cut gas price go up in killeen area per gallon at one place kari lake lay off hundred at voa parent agency amid legal battle doesnt surprise memark cuban explains why high school senior care more about making money than any generation in year cnc deadline alert rosen a longstanding law firm encourages centene corporation investor to secure counsel before important september deadline in security class action cnc bet bonus code orl bet on oregon v montana state get in bonus bet bemidji chamber ambassador welcome thrivent financial advisor letter illegal dumping and time to support wastetoenergy how the sound of name can bias hiring decision writer bloc a push for change in the u electoral college give u hope for future climate action strengthening italian finance a new era through takeover consolidation u trading partner dazed and confused after tariff court loss delaware ag other state secure americorps funding in winning suit solana etf buzz fade a investor shift to magacoin finance a rising star best soundbars with wireless rear speaker in cryptos under that could make you x richer mirroring pepe coin pepe run best small business loan option in how owner qualify compare program and secure fast funding with rok financial what happens to trump tariff now that a federal appeal court ha knocked them down cracker barrel or waffle house the south most heated food debate return amid logo saga ai cant install an hvac system why gen z is flocking to job in the trade navigating client conundrum california payday loan online same day no credit check bad credit guaranteed approval radcred launch payday loan platform for immediate financial relief for california borrower usa kari lake lay off more than staff at voice of america parent agency the washington post amazon is selling a laptop for thats nice and responsive how to check for a lien on a car before you buy how an appeal court ruling on trump tariff could upend the bond market barrons how an appeal court ruling on trump tariff could upend the bond market how to check for a lien on a car before you buy sameday business loan in fast approval for owner facing urgent cash flow need how to check for a lien on a car before you buy madison county official think wind farm could impact public safety your money way the new tax bill could impact your wallet ultimate plantbased beet burger mowest to reveal library renovation cuba energy crisis deepens a blackout grip the nation best crypto to invest in why blockdag rtx hyper and snort are gaining attention how europe is redrawing it energy map rosen global investor counsel encourages easterly rocmuni high income municipal bond fund cryptos under to accumulate now ozak ai xdc cro trx and vechain carol saline dy journalist with a story to tell about her dying powerball jackpot rise to billion sixthlargest ever sunblock charcoal and powerball holiday weekend lottery jackpot worth billion is up for grab larimer county restaurant inspection made aug china xi offer backing for myanmar sco membership bid wamco deadline notice rosen trusted investor counsel encourages western asset management company llc mutual fund investor with loss in excess of k to secure counsel before important september deadline in security class action merz promise debt relief for municipality ahead of electoral test burlington store nyseburl announces quarterly earnings result beat estimate by eps u trading partner dazed and confused after tariff court loss bloombergcom u trading partner dazed and confused after tariff court loss shopper can get electronics clothes and school supply worth up to taxfree a u state exemption final hour spirit airline bankruptcy tee up painful cut in survival bid do novelty menu like taco bell yk make investor money southwest airline begin flying first plane with secondary cockpit barrier reuters stock retail wa discussing this week and how they performed open bull mdb nvda baba channel rewind growth spark conflict video vault top wireless printer under r in paige thomason caramel pecan turtle brownie recipe dogecoin price prediction doge alternative for x gain this bull cycle billion powerball jackpot is up for grab saturday here how to play austin americanstatesman baird financial group inc acquires share of qualcomm incorporated qcom best water stock to watch now august th walmart inc wmt share purchased by titleist asset management llc deadline approach for under forty nomination eu to work on using frozen russian asset to aid ukraine after war white house to release m in americorps funding after maryland lawsuit white house to release m in americorps funding after maryland lawsuit groundbreaking of home housing cooperative in upper hammonds plain commentary lawmaker could trim electric bill baird financial group inc acquires share of ishares core sp etf ivv kodai capital management lp invests in honeywell international inc hon haberman call tariff ruling a big blow to trump agenda orange county restaurant shut down by health inspector aug costcos controversial policy change officially take effect costcos controversial policy change officially take effect mcdonalds corporation mcd share sold by baird financial group inc warren buffett warns not to invest in terrible industry because it a rewarding a struggling in quicksand micron boeing lead five stock near buy point yearold retail chain closed dozen of store s at risk in order to become the you must do what the other wont billionaire grant cardone say hard work defines success a court ha ruled most of trump tariff illegal here whats next tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury fortune promising value stock to keep an eye on august th adam thielen take pay cut with viking excited to be back home insight wealth partner llc make new investment in palantir technology inc pltr insight wealth partner llc ha holding in jpmorgan chase co jpm deeply affordable halawa rental tower nearly full best altcoins to buy this week ethereum xrp and magacoin finance highlighted after market dip letter charlotte county ha no goodpaying job young american expect to inherit on average a new survey show how much millennials and gen z are banking on family wealth buford pusser famous tennessee sheriff who inspired hollywood in the s may have killed his wife in authority say mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown a look at the race to replace canada rapidly aging fleet of submarine hilarious antivance demonstrator line up to protest his motorcade a last second turn sends them chasing car trenton raise the ukrainian flag at city hall with help from area organization photo college face financial struggle a trump policy send international enrollment plummeting college face financial struggle a trump policy send international enrollment plummeting election ejection chicago mayor and other dems are warning illegal alien ice will be at the poll we are on the street palestinian flee israel assault on gaza city cal thomas flagging flag burner again ny gov hochul now ha a press office account thats trying to outdo the newsom press office account naomi osaka call out jelena ostapenko over controversial remark toward taylor townsend ukraine exparliamentary speaker is shot dead in lviv dave bossie dnc and mamdani expose the coming disaster for democrat monday is labor day whats open whats closed wisconsin conservative supreme justice rebecca bradley wont seek reelection in fate intervenes family avoids execution in holocaust asking eric since my husband wa killed his family want nothing to do with me or my child salmo to get voter approval for new firetruck nelson trump revenge summer heat up with fed ouster bolton raid trump revenge summer heat up with fed ouster bolton raid new yorkers must fight political manipulation be it by the ccp or the united federation of teacher collegian marlboro rhinebeck resident graduate from university of rhode island tania fernandes anderson asks judge to let her dodge prison time for public corruption israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows doj call for tip on employer favoring foreign worker in hiring practice flag campaignwe cant reclaim that which wa never ours school board member say removing protection doe not give reason to bully trump cast doubt on putinzelensky meeting maybe they have to fight a little longer gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival nh democrat launch town hall series to promote presidential primary chicago mayor to sign executive order directing city to resist trump immigration raid social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows florida python hunter recount bloody battle with snake she got me son here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza got what it take to be lodis mayor for a day city accepting application from local student border czar say ice ops will ramp up for seattle portland after labor day unofficial election result strike delay start of class in southwest washington school district people are calling this jd vance habit his single most obnoxious characteristic and i have to agree epstein estate to hand over birthday book to lawmaker house dem say saturday morning college face financial struggle a trump policy send international enrollment plummeting letter something to actually feel hopeful about letter far fewer cost with votebymail election dncs summer showdown infighting expose crack in democrat unity narrative against gop agenda law enforcement increasing patrol across new hampshire over labor day weekend when can lawyer be punished for undignified or discourteous criticism of judge kellyanne conway revel in trump insane power grab after cracker barrel fiasco israel soon will halt or slow aid to northern gaza a military offensive grows ice detains somaliamerican activist ramsey county sheriff civilian officer what to know about worker over billionaire protest on labor day axios macron warns world will know by monday if putin played trump again u greenlights million sale of starlink service patriot support to ukraine state top election official balk at doj request for sensitive voter information state top election official balk at doj request for sensitive voter information when did caring for america most vulnerable kid become political opinion assembly bill undermines prop and put public safety at risk chicago plan to maintain peace amid federal deployment bondi fire doj employee over alleged gesture toward guard troop jd vance discusses readiness to be president if god forbid something happens to trump department of defense to conduct training exercise in philly starting sunday summerlins kestrel kestrel common offer unique floor plan whats open whats closed on labor day store hour for walmart costco target publix and more alcom best crypto to buy now magacoin finance gain traction a solana xrp and avax see whale inflow sen rand paul on the national debt let no one say we werent warned magax stage countdown secure your entry before the next wave begin need to save on a new appliance wayfair ha off kitchenaid mixer ninja creami did anyone win the powerball lottery jackpot swell to over billion woodside home open acacia in cadence china xi host modi and putin for summit amid anger over trump tariff daron bland contract cowboy cb agrees to massive extension with hope of returning to pro bowl form surfshark face classaction lawsuit over autorenewal violation final countdown top meme coin to invest before the next x surge hit midhudson people on the move for the week of sept nvidia lean heavily on two undisclosed customer for revenue boom china india pledge partnership ahead of putin joining summit guardian pitcher paid leave extended indefinitely a mlb continues gambling probe rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure grover norquist idea for the next gop reconciliation bill how the fed losing it independence could affect american everyday life social security and medicare cut are coming because the bond market will eventually bring congress to it knee economist say fy energy launch multilevel affiliate program to expand access to cleanpowered crypto infrastructure cardano price support now at a worried holder back altcoins with huge potential like remittix social security and medicare cut are coming because the bond market will force congress economist fortune amazon labor day sale is filled with some surprisingly good deal rosen top ranked global counsel encourages luminar technology inc investor to secure counsel before important deadline in security class action lazr bob on business fort worth ridglea theater look to reel in a buyer nvidia q ai drive growth amid revenue concentration risk lithonias recreation center to get massive renovation and upgrade crypto news ozak ai presale heat up with m raisednext x token tesla unexpectedly end contract at giga texas letting go people tesla unexpectedly end contract at giga texas letting go people electrek gen z shift to aiproof trade like plumbing for job security business brief postal carrier retires after almost year of service intel secures b accelerated chip funding with u equity stake u still working on trade deal despite court ruling ustr say trump tariff spark pricing chaos for u business six month in vintage photo show how the role of woman in the workforce ha evolved in the last year i felt like a dead person former goldman sachs banker said before leaving u to build a startup in seoul which store and restaurant will be open for labor day should you ignore ethereum and buy this surging altcoin instead best samsung phone under r in budget pick that deliver hbar price set for gain in q a one altcoin could make investor over x by november future why trump tariff ruling may not matter for stock investor business daily touted a the teslakiller lucid scramble to stay on the nasdaq kemp jones reaped big money from company with an interest in legislation kemp jones reaped big money from company with an interest in legislation builderais b rise and collapse highlight fragility of ai boom seeking alpha kemp jones reaped big money from company with an interest in legislation final chance to get cash bonus from major u bank putting away a day will secure it for you people still spending on tech despite red flag in july report gizmodo people still spending on tech despite red flag in july report popular weightloss stock make a massive heartsaving claim trump trade counselor peter navarro rebuke politician in black robe over partisan tariff ruling mindanao busine</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>hows the market doe ownership go past the topsoil fresh stock on jim cramers radar juneteenth organizer get funding to repair modernize building panda express owns other restaurant chain do you know which one fed rate cut still on track no firework after nvidia earnings federal government post billion deficit from april to june canada whats going on with broadcom stock friday oakland unified school district looking to shed nearly million from budget is it a bot or not ticketings next big legal fight could reshape the resale industry a model for understanding with edward kaplan smlr investor have opportunity to lead semler scientific inc security fraud lawsuit first filed by the rosen law firm rock tech lithium announces offering of up to million the persistent pitfall of taxpayer funded campaign berkshire hillsbrookline merger nears completion retailer warn trump tariff will trigger consumer price explosion who will he blame boing boing nvidia ceo say ai will actually make u busier in the future gizmodo is amazon falling behind in the cloud computing battle brutally honest way to finance your startup dmv may owe you s and have no obligation to let you know wa being held in just a single case qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada should the federal reserve cut rate next month should the federal reserve cut rate next month hope gas responds to criticism in it pipeline program ratehike case raising cane to open ann arbor location september th the company second in metro detroit trump administration kill wasteful funding for humboldt bay offshore wind project sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion ardot seeking public comment on proposed disadvantaged business enterprise goal for why you should think twice before buying private equity in your k nasb financial inc declares cash dividend on common stock sunblock charcoal and powerball holiday weekend lottery drawing worth billion ap news ulta beauty delivers strong quarter investor brush off the glow thought i wa going to die tunisian singer detained for week fight deportation while trying to finish music small business joint venture win coast guard cyber contract dupont to sell kevlar business for billion the manufacturer life insurance company grows position in tesla inc tsla stock market news today market slide a chip stock weigh spsp complete index seeking alpha layoff hit international paper jb hunt hormel and more the orange peel first year put asheville on the map now staffer hope to buy it cv walgreens now require prescription for covid vaccine in colorado the denver post in hong kong eric trump lauds growing influence of crypto the new york time forecasting the future analyst projection for oneok what the option market tell u about mastercard lazr investor have opportunity to lead luminar technology inc security fraud lawsuit sword group availability of the h financial report sword group h report of the liquidity agreement contracted with oddo bhf procter gamble unusual option activity forecasting the future analyst projection for dt midstream dows option frenzy what you need to know pce inflation flat but core sticky implication for fed september meeting analyst expectation for targa resourcess future breaking down karooooo analyst share their view segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase a glimpse into the expert outlook on cheniere energy through analyst is rivian automotive gaining or losing market support peering into extreme networkss recent short interest let talk indianola kwik star ribbon cutting expert outlook snapon through the eye of analyst is flex gaining or losing market support pe ratio insight for bank of nova scotia let talk knoxville planning and zoning administrator nathan parch part two segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase u government publishes gdp data on bitcoin ethereum blockchains home price in okanagan and kamloops area may be levelling housewise chainlink link price movement face hurdle litecoin target rally while cold wallet hold roi edge major discount on outdoor furniture costway dining set off at target bytedance hit b valuation a q revenue surge to b energy exchange electronx earns cftc designated market and clearing approval how senior can borrow home equity without refinancing now crypto news today coinshares profit jump avalanche transaction rise gumi add xrp here why serve robotics surged this week savvy shopper save over k in year by extreme couponing she scored k of jcpenney cookware for just backtoschool sale tax holiday the edmund fitzgerald and a state microbe theyre among state bill in august should you buy lucid stock ahead of it for reverse stock split bitcoin drop below a xrp slide below and eth dogecoin wobble shopping labor day furniture sale tip to bargain for the best price ollies bargain earnings suggest analyst underestimate longterm potential no ruling friday on trump attempt to fire fed official the credit race closing the perception gap to win welcome to the new made in china era and it look a lot different dell struggle to protect margin a supply chain cost mount cracker barrel ditched it new logo but it also got rid of something else labubu doll and affordable latte why chinese brand are betting big on the u business insider mycarrier portal and carrier assure integrate to make carrier vetting easier cracker barrel is still deep in dei despite the return of uncle herschel former trans mountain ceo to head major project office canada cracker barrel did more than just ditch it logo after maga meltdown the daily beast cracker barrel new logo wa pitiful one of chain original executive say anthony brown maryland legal victory show prudent use of resource reader commentary atlanta becomes largest u metro without a printed daily newspaper a journalconstitution go digital techstock skid sends nasdaq sharply lower live stockmarket update understanding the benefit and risk of ai agent university of northern iowa to open finance and real estate analytics lab for business eli lilly is proof that wall street star dont have to be tech titan trump fire democratic member from transportation board just before it considers the largest railroad merger in history marvell sink a weak data center outlook stokes custom ai chip worry reuters mount logan capital inc shareholder approve previously announced business combination with degree capital corp court block trump effort to end protected status for venezuelan mamdani team with sharpton to threaten wall street upcoming upgrade to holocaust museum exhibit spark some staff concern source trump planning immigration crackdown in chicago next week dhs source say gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber migrant defer their american dream to seek asylum in mexico bonus editorial cartoon for aug alabama town first black mayor reelected after being locked out of office lawyer who led karen read defense one step closer to joining team for civil suit trump move to cut bn in foreign aid already approved by congress rubio revoke visa for palestinian official denying address at un meeting alabama town first black mayor reelected year after he say white resident locked him out of office cbs news can tv help prepare for invasion jd vance say there thing dems should learn from trump and critic cant believe he serious jd vance say there thing dems should learn from trump and critic cant believe he serious abrego garcia asks for gag order on bondi noem meet bill pulte the trump housing official at the center of the latest fed controversy abrego garcia asks for gag order on bondi noem judge weighs request to block trump firing of fed governor lisa cook abrego garcia asks for gag order on bondi noem contract talk fail between alberta government and teacher possible strike loom alberta republican joni ernst will not seek reelection source say abrego garcia asks for gag order on bondi noem trump yank kamala harris bidenextended taxpayerfunded secret service protection before book tour susan estrich the epitome of dumbness judge hears argument on lisa cook attempted firing by trump administration psc answer preston county commission objection to marl project corruption allegation impact argentina president mileis popularity trump block b in foreign aid congress okd using maneuver last seen nearly year ago trump block b in foreign aid congress okd using maneuver last seen nearly year ago mackinac island police chief to resign citing ongoing friction with city council a lament for the shrinking middle class reader commentary dear annie unfaithful fiancee tell me to stop living in the past appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan a trumpbrokered peace deal in the south caucasus is hopeful but incomplete many state employeefriendly labor law take effect a nlrb remains quorumless benton county to display in god we trust in all public building by oct everyone on x point and laugh at dingus gungrabber who share pic of bullet scattered on his street democrat some republican cry outrage over trump use of rare tactic to withhold approved foreign aid funding lori falce year of thought and prayer appeal court say uk asylumseekers can stay at hotel dc federal judge to weigh order blocking fed gov lisa cook firing ahead of interest rate meeting let talk knoxville planning and zoning administrator nathan parch part two donald trump war on culture is not a sideshow japan india to deepen security economic tie amid u tariff ai is ummasking ice officer can washington do anything about it politico public trust in election increase with clear fact sen ernst of iowa is expected to announce next month that she wont run for reelection in u revoke visa of palestinian official ahead of un general assembly fox news star call out trump ally over apparent hypocrisy this is the same thing sen ernst of iowa is expected to announce next month that she wont run for reelection in ap news fox news star call out trump ally over apparent hypocrisy this is the same thing free speech unmuted president trump executive order on flag desecration it a joke san jose mayor slam california legislature over lack of prop funding ransomware attack targeting pa attorney general lead to case delay susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider chicago is in the trump administration sight for it next immigration crackdown chicago is in the trump administration sight for it next immigration crackdown trump admin plan immigration enforcement surge in boston politico a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows kilmar abrego garcia asks for gag order against pam bondi kristi noem kilmar abrego garcia asks for gag order against pam bondi kristi noem texas gov greg abbott sign new congressional redistricting map president trump requested kimball shinkoskey explain the law talk for trump riviera in gaza persist a israel push deeper into gaza city france germany vow to up pressure on ogre putin bankruptcy for north dakota and western minnesota published aug trump administration to cut plus job at voice of america best business line of credit in flexible small business funding option for growth and emergency adhesive dowel veneer the industrial choice shaping mass timber verizon down how to fix so modeonly issue in phone amid outage hindustan time hindustan time what would the fed do in a tie vote it not clear and the bank of england had to break a deadlock this month can you use milwaukee battery on harbor freight tool ulster county rail trail study to be contracted to new paltzbased consulting firm tim walz admits vp bid might have hurt him with voter in home state judge delay septum rate increase additional service cut gas price go up in killeen area per gallon at one place kari lake lay off hundred at voa parent agency amid legal battle doesnt surprise memark cuban explains why high school senior care more about making money than any generation in year cnc deadline alert rosen a longstanding law firm encourages centene corporation investor to secure counsel before important september deadline in security class action cnc bet bonus code orl bet on oregon v montana state get in bonus bet bemidji chamber ambassador welcome thrivent financial advisor letter illegal dumping and time to support wastetoenergy how the sound of name can bias hiring decision writer bloc a push for change in the u electoral college give u hope for future climate action strengthening italian finance a new era through takeover consolidation u trading partner dazed and confused after tariff court loss delaware ag other state secure americorps funding in winning suit solana etf buzz fade a investor shift to magacoin finance a rising star best soundbars with wireless rear speaker in cryptos under that could make you x richer mirroring pepe coin pepe run best small business loan option in how owner qualify compare program and secure fast funding with rok financial what happens to trump tariff now that a federal appeal court ha knocked them down cracker barrel or waffle house the south most heated food debate return amid logo saga ai cant install an hvac system why gen z is flocking to job in the trade navigating client conundrum california payday loan online same day no credit check bad credit guaranteed approval radcred launch payday loan platform for immediate financial relief for california borrower usa kari lake lay off more than staff at voice of america parent agency the washington post amazon is selling a laptop for thats nice and responsive how to check for a lien on a car before you buy how an appeal court ruling on trump tariff could upend the bond market barrons how an appeal court ruling on trump tariff could upend the bond market how to check for a lien on a car before you buy sameday business loan in fast approval for owner facing urgent cash flow need how to check for a lien on a car before you buy madison county official think wind farm could impact public safety your money way the new tax bill could impact your wallet ultimate plantbased beet burger mowest to reveal library renovation cuba energy crisis deepens a blackout grip the nation best crypto to invest in why blockdag rtx hyper and snort are gaining attention how europe is redrawing it energy map rosen global investor counsel encourages easterly rocmuni high income municipal bond fund cryptos under to accumulate now ozak ai xdc cro trx and vechain carol saline dy journalist with a story to tell about her dying powerball jackpot rise to billion sixthlargest ever sunblock charcoal and powerball holiday weekend lottery jackpot worth billion is up for grab larimer county restaurant inspection made aug china xi offer backing for myanmar sco membership bid wamco deadline notice rosen trusted investor counsel encourages western asset management company llc mutual fund investor with loss in excess of k to secure counsel before important september deadline in security class action merz promise debt relief for municipality ahead of electoral test burlington store nyseburl announces quarterly earnings result beat estimate by eps u trading partner dazed and confused after tariff court loss bloombergcom u trading partner dazed and confused after tariff court loss shopper can get electronics clothes and school supply worth up to taxfree a u state exemption final hour spirit airline bankruptcy tee up painful cut in survival bid do novelty menu like taco bell yk make investor money southwest airline begin flying first plane with secondary cockpit barrier reuters stock retail wa discussing this week and how they performed open bull mdb nvda baba channel rewind growth spark conflict video vault top wireless printer under r in paige thomason caramel pecan turtle brownie recipe dogecoin price prediction doge alternative for x gain this bull cycle billion powerball jackpot is up for grab saturday here how to play austin americanstatesman baird financial group inc acquires share of qualcomm incorporated qcom best water stock to watch now august th walmart inc wmt share purchased by titleist asset management llc deadline approach for under forty nomination eu to work on using frozen russian asset to aid ukraine after war white house to release m in americorps funding after maryland lawsuit white house to release m in americorps funding after maryland lawsuit groundbreaking of home housing cooperative in upper hammonds plain commentary lawmaker could trim electric bill baird financial group inc acquires share of ishares core sp etf ivv kodai capital management lp invests in honeywell international inc hon haberman call tariff ruling a big blow to trump agenda orange county restaurant shut down by health inspector aug costcos controversial policy change officially take effect costcos controversial policy change officially take effect mcdonalds corporation mcd share sold by baird financial group inc warren buffett warns not to invest in terrible industry because it a rewarding a struggling in quicksand micron boeing lead five stock near buy point yearold retail chain closed dozen of store s at risk in order to become the you must do what the other wont billionaire grant cardone say hard work defines success a court ha ruled most of trump tariff illegal here whats next tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury fortune promising value stock to keep an eye on august th adam thielen take pay cut with viking excited to be back home insight wealth partner llc make new investment in palantir technology inc pltr insight wealth partner llc ha holding in jpmorgan chase co jpm deeply affordable halawa rental tower nearly full best altcoins to buy this week ethereum xrp and magacoin finance highlighted after market dip letter charlotte county ha no goodpaying job young american expect to inherit on average a new survey show how much millennials and gen z are banking on family wealth buford pusser famous tennessee sheriff who inspired hollywood in the s may have killed his wife in authority say mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown a look at the race to replace canada rapidly aging fleet of submarine hilarious antivance demonstrator line up to protest his motorcade a last second turn sends them chasing car trenton raise the ukrainian flag at city hall with help from area organization photo college face financial struggle a trump policy send international enrollment plummeting college face financial struggle a trump policy send international enrollment plummeting election ejection chicago mayor and other dems are warning illegal alien ice will be at the poll we are on the street palestinian flee israel assault on gaza city cal thomas flagging flag burner again ny gov hochul now ha a press office account thats trying to outdo the newsom press office account naomi osaka call out jelena ostapenko over controversial remark toward taylor townsend ukraine exparliamentary speaker is shot dead in lviv dave bossie dnc and mamdani expose the coming disaster for democrat monday is labor day whats open whats closed wisconsin conservative supreme justice rebecca bradley wont seek reelection in fate intervenes family avoids execution in holocaust asking eric since my husband wa killed his family want nothing to do with me or my child salmo to get voter approval for new firetruck nelson trump revenge summer heat up with fed ouster bolton raid trump revenge summer heat up with fed ouster bolton raid new yorkers must fight political manipulation be it by the ccp or the united federation of teacher collegian marlboro rhinebeck resident graduate from university of rhode island tania fernandes anderson asks judge to let her dodge prison time for public corruption israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows doj call for tip on employer favoring foreign worker in hiring practice flag campaignwe cant reclaim that which wa never ours school board member say removing protection doe not give reason to bully trump cast doubt on putinzelensky meeting maybe they have to fight a little longer gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival nh democrat launch town hall series to promote presidential primary chicago mayor to sign executive order directing city to resist trump immigration raid social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows florida python hunter recount bloody battle with snake she got me son here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza got what it take to be lodis mayor for a day city accepting application from local student border czar say ice ops will ramp up for seattle portland after labor day unofficial election result strike delay start of class in southwest washington school district people are calling this jd vance habit his single most obnoxious characteristic and i have to agree epstein estate to hand over birthday book to lawmaker house dem say saturday morning college face financial struggle a trump policy send international enrollment plummeting letter something to actually feel hopeful about letter far fewer cost with votebymail election dncs summer showdown infighting expose crack in democrat unity narrative against gop agenda law enforcement increasing patrol across new hampshire over labor day weekend when can lawyer be punished for undignified or discourteous criticism of judge kellyanne conway revel in trump insane power grab after cracker barrel fiasco israel soon will halt or slow aid to northern gaza a military offensive grows ice detains somaliamerican activist ramsey county sheriff civilian officer what to know about worker over billionaire protest on labor day axios macron warns world will know by monday if putin played trump again u greenlights million sale of starlink service patriot support to ukraine state top election official balk at doj request for sensitive voter information state top election official balk at doj request for sensitive voter information when did caring for america most vulnerable kid become political opinion assembly bill undermines prop and put public safety at risk chicago plan to maintain peace amid federal deployment bondi fire doj employee over alleged gesture toward guard troop jd vance discusses readiness to be president if god forbid something happens to trump department of defense to conduct training exercise in philly starting sunday summerlins kestrel kestrel common offer unique floor plan whats open whats closed on labor day store hour for walmart costco target publix and more alcom best crypto to buy now magacoin finance gain traction a solana xrp and avax see whale inflow sen rand paul on the national debt let no one say we werent warned magax stage countdown secure your entry before the next wave begin need to save on a new appliance wayfair ha off kitchenaid mixer ninja creami did anyone win the powerball lottery jackpot swell to over billion woodside home open acacia in cadence china xi host modi and putin for summit amid anger over trump tariff daron bland contract cowboy cb agrees to massive extension with hope of returning to pro bowl form surfshark face classaction lawsuit over autorenewal violation final countdown top meme coin to invest before the next x surge hit midhudson people on the move for the week of sept nvidia lean heavily on two undisclosed customer for revenue boom china india pledge partnership ahead of putin joining summit guardian pitcher paid leave extended indefinitely a mlb continues gambling probe rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure grover norquist idea for the next gop reconciliation bill how the fed losing it independence could affect american everyday life social security and medicare cut are coming because the bond market will eventually bring congress to it knee economist say fy energy launch multilevel affiliate program to expand access to cleanpowered crypto infrastructure cardano price support now at a worried holder back altcoins with huge potential like remittix social security and medicare cut are coming because the bond market will force congress economist fortune amazon labor day sale is filled with some surprisingly good deal rosen top ranked global counsel encourages luminar technology inc investor to secure counsel before important deadline in security class action lazr bob on business fort worth ridglea theater look to reel in a buyer nvidia q ai drive growth amid revenue concentration risk lithonias recreation center to get massive renovation and upgrade crypto news ozak ai presale heat up with m raisednext x token tesla unexpectedly end contract at giga texas letting go people tesla unexpectedly end contract at giga texas letting go people electrek gen z shift to aiproof trade like plumbing for job security business brief postal carrier retires after almost year of service intel secures b accelerated chip funding with u equity stake u still working on trade deal despite court ruling ustr say trump tariff spark pricing chaos for u business six month in vintage photo show how the role of woman in the workforce ha evolved in the last year i felt like a dead person former goldman sachs banker said before leaving u to build a startup in seoul which store and restaurant will be open for labor day should you ignore ethereum and buy this surging altcoin instead best samsung phone under r in budget pick that deliver hbar price set for gain in q a one altcoin could make investor over x by november future why trump tariff ruling may not matter for stock investor business daily touted a the teslakiller lucid scramble to stay on the nasdaq kemp jones reaped big money from company with an interest in legislation kemp jones reaped big money from company with an interest in legislation builderais b rise and collapse highlight fragility of ai boom seeking alpha kemp jones reaped big money from company with an interest in legislation final chance to get cash bonus from major u bank putting away a day will secure it for you people still spending on tech despite red flag in july report gizmodo people still spending on tech despite red flag in july report popular weightloss stock make a massive heartsaving claim trump trade counselor peter navarro rebuke politician in black robe over partisan tariff ruling mindanao busine</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.9987</v>
+      </c>
+      <c r="O49" t="n">
+        <v>190</v>
+      </c>
+      <c r="P49" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>305</v>
+      </c>
+      <c r="S49" t="n">
+        <v>171</v>
+      </c>
+      <c r="T49" t="n">
+        <v>461</v>
+      </c>
+      <c r="U49" t="n">
+        <v>272</v>
+      </c>
+      <c r="V49" t="n">
+        <v>101</v>
+      </c>
+      <c r="W49" t="n">
+        <v>87</v>
+      </c>
+      <c r="X49" t="n">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/stock_news_tone.xlsx
+++ b/notebooks/stock_news_tone.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4284,6 +4284,84 @@
         <v>133</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6448.259765625</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6453.669921875</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6416.169921875</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6445.81982421875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4465360000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0051000736279842</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>the winklevoss twin are eyeing billion crypto ipo trump cant use national guard military in california to enforce law judge breyer rule family of max crash victim push to appoint a special prosecutor saying boeing is trying to buy everyone off gold smash record a ratecut bet policy turmoil fuel haven rush coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war palantir stock struggle a valuation criticism and ceo sale weigh on investor coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war turkiyes huge summer of transfer explained how galatasaray and fenerbahce can outspend europe big club anthropic nearly triple valuation to b with massive new funding disney to pay million over alleged violation of childrens online privacy army pick startup to fasttrack selfdriving squad vehicle ai chatbots for doctor are hot but there plenty of value down the stack too argues corti ceo genesee county architecture firm selects yearold batavia house for new hq hundred of economist defend lisa cook fed independence in open letter against trump effort coming price cut at mcdonalds may signal a broader fast food price war a trump tariff struggle in the court there a simple solution he could consider top trending topic of august the less independent the fed is the more the yield curve will steepen national alliance brenner sap to invest billion in europe sovereign cloud anna wintour tap chloe malle a vogue successor but shes still in charge marcus where you are and where youve been stock are experiencing a healthy reset say citis drew pettit ubs give america a recession checkup and see a probability from the hard data with a soggy economy ahead fortune mcdonalds will launch new value meal on monday sept mcdonalds will launch new value meal on monday sept amazon end a program that let prime member share free shipping perk with user outside household amazon end a program that let prime member share free shipping perk with user outside household general assembly looking to reinvigorate staterun venture capital fund fi deadline rosen leading investor counsel encourages fiserv inc investor with loss in excess of k to secure counsel before important deadline in security class action fi trifork group reporting of transaction made by person discharging managerial responsibility clean any screen or lens with the infinitely reuseable waterbear screen cleaner exbudget staffer weigh in against trump pocket rescission offstrip casino team up with new bookmaker proposed budget for west aurora school district show million surplus save big on top gaming gear from walmart now score headset laptop desktop more company kick off ipo roadshow market rally still ha room to run where to invest what are analytical insight wet strength resin market to reach u million by astute analytica blue apron pivot amid our subscription fatigue coreweave stock crwv sink a insider sell at an alarming pace tipranks kraft heinz to separate into two publicly traded company predoc raise million for aipowered health information management system space stock tracker trump move space command rocket lab open launch complex crocs appoints nike alum to cfo chair coreweave tumble a top shareholder magnetar dial down position put on huge collar trade sherwood news bitcoin buck stock market downtrend but lag gold rally congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process solana early investor who bought at and exited at ath belief only new crypto can repeat sol rise congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process openai and meta say theyre fixing ai chatbots to better respond to teen in distress openai and meta say theyre fixing ai chatbots to better respond to teen in distress costco told to review footage after store manager blatantly accused shopper of ignoring strict store policy nestle dismisses ceo over undisclosed relationship with subordinate nestle dismisses ceo over undisclosed relationship with subordinate egg milk bread all rising a summer close royce microcap trust nyse rmt a of jul how low will mortgage rate fall with a september fed rate cut here what to know trump and son stake in crypto firm worth bn the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way tesla trillion secret musk say robot could be of it value coming price cut at mcdonalds may signal a broader fast food price war stafford co mull zoning regulation government shutdown on oct seen a increasingly likely exclusive disney will pay m to settle childrens privacy lawsuit with ftc axios ace hardware crave cooky among new business in sugar landmissouri city bet bonus code njcom unlock a guaranteed bonus for mlb u open today syndeo medical announces multiyear exclusive distribution agreement for bearpacs passiotm pump drainage system irbt deadline rosen recognized investor counsel encourages irobot corporation investor with loss in excess of k to secure counsel before important september deadline in security class action irbt the white house premium how washington is creating ai stock rocket openai shuffle executive role acquires statsig for billion openai shuffle executive role acquires statsig for billion the verge salesforce advantage over hubspot and mondaycom highlight relative valuation an expanded version of the dol opinion letter program return what do retail employer need to know jefferies david katz bullish call for cruise maryland man collect his second big lottery prize in two month elliott management look to put fizz back into pepsi with b stake a it press for a turnaround amazon prime signups reportedly lagged in u leading up to annual sale event pennsylvania democrat attract some buzz in the party bid to take back u house turn out trump cant turn activeduty troop into police officer after losing two antiviolence worker to gunfire chicago nonprofit persists we have to be strong why is bangladesh saying it can no longer host rohingya school shouldnt wait for legislature to ban cellphone use the republican editorial pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge why are our church no longer safe annunciation school shooting raise alarming question letter to the editor sen joni ernst will not run for reelection in live now gop hold press conference on federal authority over dc a trump tariff struggle in the court there a simple solution he could consider trump tariff decision an emergency will appeal a soon a wednesday axios what america should know about wes moore guest commentary gov healey slam republic service over stalled trash strike talk kim jong un daughter and possible heir make rare foreign appearance poll what should be the new massachusetts flag the judge who defied trump now face brazil biggest case what is the posse comitatus act yearold law governs military role in local law enforcement voter registration trend unchanged at traditional summer end cimg inc completes the previously announced sale of million of it common stock for bitcoin pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge tim walz appears to tell supporter all is not lost because trump will die soon watch profane rashida tlaib rant target israel backer in wild unhinged tirade how much ha your devon county councillor spent in their community so far british wife of trump voter face deportation after year in u amid immigration crackdown saga education launch tutoring partnership with brooklyn lab to accelerate math learning a life lived herman lyon carried the horror of war with strength and courage harford council district f incumbent jacob bennett run for reelection harford council district f incumbent jacob bennett run for reelection tv writer graham linehans arrest over transgender post spark free speech outcry in the uk tv writer graham linehans arrest over transgender post spark free speech outcry in the uk gop rep thomas massie take first step to force a vote on releasing the epstein file texas dei ban expands to public school face federal lawsuit u drone strike cartel drug boat trump post video for world to see beware uk comedy writer graham linehan arrested over social medium post criticizing trans activist gavin newsom brutally taunt trump after major legal victory trump face new epstein headache a congress return from recess israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive airbnb cofounder share when he lost faith in dem party switched to gop israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive springfield garden could be banned from owning managing property in mass ag campbell say what is a pardon and who is eligible wichita criminal defense lawyer who will replace jerry nadler who will retire in after year in congress repping manhattan looking back on japan surrender in wwii year later trump expected to speak shortly a majority of nevada legislation aimed at government transparency failed during the session in the martian author david baron explores mar mania of the th century israel continues to intensify offensive in gaza city rep jerry nadler announces retirement citing bidens oneterm presidency politico ussfcu win dual honor at broadcom customer achievement award trial of greensboro native accused of attempting to assassinate trump set for sept court annuls istanbul congress of turkey main opposition party dismisses leadership court annuls istanbul congress of turkey main opposition party dismisses leadership ernst wont seek reelection giving democrat opening in battle for senate israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge madness in minneapolis court allows trump admin close in on yanking back bidens gold bar pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge delray beach argues to keep it rainbow intersection at hearing in orlando delray beach argues to keep it rainbow intersection at hearing in orlando judge dismisses lawsuit springfield joined over terminated m epa grant labor day protester across the country demand worker right decry ice labor day protester across the country demand worker right decry ice</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>the winklevoss twin are eyeing billion crypto ipo trump cant use national guard military in california to enforce law judge breyer rule family of max crash victim push to appoint a special prosecutor saying boeing is trying to buy everyone off gold smash record a ratecut bet policy turmoil fuel haven rush coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war palantir stock struggle a valuation criticism and ceo sale weigh on investor coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war turkiyes huge summer of transfer explained how galatasaray and fenerbahce can outspend europe big club anthropic nearly triple valuation to b with massive new funding disney to pay million over alleged violation of childrens online privacy army pick startup to fasttrack selfdriving squad vehicle ai chatbots for doctor are hot but there plenty of value down the stack too argues corti ceo genesee county architecture firm selects yearold batavia house for new hq hundred of economist defend lisa cook fed independence in open letter against trump effort coming price cut at mcdonalds may signal a broader fast food price war a trump tariff struggle in the court there a simple solution he could consider top trending topic of august the less independent the fed is the more the yield curve will steepen national alliance brenner sap to invest billion in europe sovereign cloud anna wintour tap chloe malle a vogue successor but shes still in charge marcus where you are and where youve been stock are experiencing a healthy reset say citis drew pettit ubs give america a recession checkup and see a probability from the hard data with a soggy economy ahead fortune mcdonalds will launch new value meal on monday sept mcdonalds will launch new value meal on monday sept amazon end a program that let prime member share free shipping perk with user outside household amazon end a program that let prime member share free shipping perk with user outside household general assembly looking to reinvigorate staterun venture capital fund fi deadline rosen leading investor counsel encourages fiserv inc investor with loss in excess of k to secure counsel before important deadline in security class action fi trifork group reporting of transaction made by person discharging managerial responsibility clean any screen or lens with the infinitely reuseable waterbear screen cleaner exbudget staffer weigh in against trump pocket rescission offstrip casino team up with new bookmaker proposed budget for west aurora school district show million surplus save big on top gaming gear from walmart now score headset laptop desktop more company kick off ipo roadshow market rally still ha room to run where to invest what are analytical insight wet strength resin market to reach u million by astute analytica blue apron pivot amid our subscription fatigue coreweave stock crwv sink a insider sell at an alarming pace tipranks kraft heinz to separate into two publicly traded company predoc raise million for aipowered health information management system space stock tracker trump move space command rocket lab open launch complex crocs appoints nike alum to cfo chair coreweave tumble a top shareholder magnetar dial down position put on huge collar trade sherwood news bitcoin buck stock market downtrend but lag gold rally congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process solana early investor who bought at and exited at ath belief only new crypto can repeat sol rise congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process openai and meta say theyre fixing ai chatbots to better respond to teen in distress openai and meta say theyre fixing ai chatbots to better respond to teen in distress costco told to review footage after store manager blatantly accused shopper of ignoring strict store policy nestle dismisses ceo over undisclosed relationship with subordinate nestle dismisses ceo over undisclosed relationship with subordinate egg milk bread all rising a summer close royce microcap trust nyse rmt a of jul how low will mortgage rate fall with a september fed rate cut here what to know trump and son stake in crypto firm worth bn the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way tesla trillion secret musk say robot could be of it value coming price cut at mcdonalds may signal a broader fast food price war stafford co mull zoning regulation government shutdown on oct seen a increasingly likely exclusive disney will pay m to settle childrens privacy lawsuit with ftc axios ace hardware crave cooky among new business in sugar landmissouri city bet bonus code njcom unlock a guaranteed bonus for mlb u open today syndeo medical announces multiyear exclusive distribution agreement for bearpacs passiotm pump drainage system irbt deadline rosen recognized investor counsel encourages irobot corporation investor with loss in excess of k to secure counsel before important september deadline in security class action irbt the white house premium how washington is creating ai stock rocket openai shuffle executive role acquires statsig for billion openai shuffle executive role acquires statsig for billion the verge salesforce advantage over hubspot and mondaycom highlight relative valuation an expanded version of the dol opinion letter program return what do retail employer need to know jefferies david katz bullish call for cruise maryland man collect his second big lottery prize in two month elliott management look to put fizz back into pepsi with b stake a it press for a turnaround amazon prime signups reportedly lagged in u leading up to annual sale event pennsylvania democrat attract some buzz in the party bid to take back u house turn out trump cant turn activeduty troop into police officer after losing two antiviolence worker to gunfire chicago nonprofit persists we have to be strong why is bangladesh saying it can no longer host rohingya school shouldnt wait for legislature to ban cellphone use the republican editorial pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge why are our church no longer safe annunciation school shooting raise alarming question letter to the editor sen joni ernst will not run for reelection in live now gop hold press conference on federal authority over dc a trump tariff struggle in the court there a simple solution he could consider trump tariff decision an emergency will appeal a soon a wednesday axios what america should know about wes moore guest commentary gov healey slam republic service over stalled trash strike talk kim jong un daughter and possible heir make rare foreign appearance poll what should be the new massachusetts flag the judge who defied trump now face brazil biggest case what is the posse comitatus act yearold law governs military role in local law enforcement voter registration trend unchanged at traditional summer end cimg inc completes the previously announced sale of million of it common stock for bitcoin pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge tim walz appears to tell supporter all is not lost because trump will die soon watch profane rashida tlaib rant target israel backer in wild unhinged tirade how much ha your devon county councillor spent in their community so far british wife of trump voter face deportation after year in u amid immigration crackdown saga education launch tutoring partnership with brooklyn lab to accelerate math learning a life lived herman lyon carried the horror of war with strength and courage harford council district f incumbent jacob bennett run for reelection harford council district f incumbent jacob bennett run for reelection tv writer graham linehans arrest over transgender post spark free speech outcry in the uk tv writer graham linehans arrest over transgender post spark free speech outcry in the uk gop rep thomas massie take first step to force a vote on releasing the epstein file texas dei ban expands to public school face federal lawsuit u drone strike cartel drug boat trump post video for world to see beware uk comedy writer graham linehan arrested over social medium post criticizing trans activist gavin newsom brutally taunt trump after major legal victory trump face new epstein headache a congress return from recess israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive airbnb cofounder share when he lost faith in dem party switched to gop israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive springfield garden could be banned from owning managing property in mass ag campbell say what is a pardon and who is eligible wichita criminal defense lawyer who will replace jerry nadler who will retire in after year in congress repping manhattan looking back on japan surrender in wwii year later trump expected to speak shortly a majority of nevada legislation aimed at government transparency failed during the session in the martian author david baron explores mar mania of the th century israel continues to intensify offensive in gaza city rep jerry nadler announces retirement citing bidens oneterm presidency politico ussfcu win dual honor at broadcom customer achievement award trial of greensboro native accused of attempting to assassinate trump set for sept court annuls istanbul congress of turkey main opposition party dismisses leadership court annuls istanbul congress of turkey main opposition party dismisses leadership ernst wont seek reelection giving democrat opening in battle for senate israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge madness in minneapolis court allows trump admin close in on yanking back bidens gold bar pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge delray beach argues to keep it rainbow intersection at hearing in orlando delray beach argues to keep it rainbow intersection at hearing in orlando judge dismisses lawsuit springfield joined over terminated m epa grant labor day protester across the country demand worker right decry ice labor day protester across the country demand worker right decry ice</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-0.9968</v>
+      </c>
+      <c r="O50" t="n">
+        <v>130</v>
+      </c>
+      <c r="P50" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>170</v>
+      </c>
+      <c r="S50" t="n">
+        <v>61</v>
+      </c>
+      <c r="T50" t="n">
+        <v>163</v>
+      </c>
+      <c r="U50" t="n">
+        <v>182</v>
+      </c>
+      <c r="V50" t="n">
+        <v>32</v>
+      </c>
+      <c r="W50" t="n">
+        <v>79</v>
+      </c>
+      <c r="X50" t="n">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
